--- a/Assets/AddressableResource/Data/Excels/TowerWeaponLevelData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/TowerWeaponLevelData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53ADB77C-7CB2-4D1F-8254-633CDE1A35EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA416B52-32DA-417E-9B0C-05ADCA7EB058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="179" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -197,7 +197,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">

--- a/Assets/AddressableResource/Data/Excels/TowerWeaponLevelData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/TowerWeaponLevelData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA416B52-32DA-417E-9B0C-05ADCA7EB058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC9F40C-E176-4E00-9615-18DE7A82BB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="12">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" ref="I2" si="0">SUM(B2:D2)</f>
@@ -594,7 +594,7 @@
       </c>
       <c r="M2" s="4">
         <f>G2</f>
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="XFB2" s="15"/>
     </row>
@@ -615,11 +615,11 @@
         <v>1</v>
       </c>
       <c r="F3" s="1">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="G3" s="12">
-        <f>150+A3*2</f>
-        <v>152</v>
+        <f>150+ROUNDUP(A3*3.5,0)</f>
+        <v>154</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I34" si="3">SUM(B3:D3)</f>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" s="4">
         <f>G3</f>
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
@@ -663,429 +663,429 @@
         <v>2</v>
       </c>
       <c r="F4" s="13">
-        <f>F3+0.005</f>
-        <v>1.4999999999999999E-2</v>
+        <f>F3+0.01</f>
+        <v>0.21000000000000002</v>
       </c>
       <c r="G4" s="12">
-        <f t="shared" ref="G4:G41" si="5">150+A4*2</f>
-        <v>154</v>
+        <f>150+ROUNDUP(A4*3.5,0)+ROUNDUP(G3/3,0)</f>
+        <v>209</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J4" s="14">
-        <f t="shared" ref="J4:J67" si="6">B4/10000</f>
+        <f t="shared" ref="J4:J67" si="5">B4/10000</f>
         <v>0.9</v>
       </c>
       <c r="K4" s="14">
-        <f t="shared" ref="K4:K67" si="7">C4/10000</f>
+        <f t="shared" ref="K4:K67" si="6">C4/10000</f>
         <v>0.1</v>
       </c>
       <c r="L4" s="14">
-        <f t="shared" ref="L4:L67" si="8">D4/10000</f>
+        <f t="shared" ref="L4:L67" si="7">D4/10000</f>
         <v>0</v>
       </c>
       <c r="M4" s="4">
-        <f t="shared" ref="M4:M67" si="9">G4</f>
-        <v>154</v>
+        <f t="shared" ref="M4:M67" si="8">G4</f>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <f t="shared" ref="A5:A68" si="10">A4+1</f>
+        <f t="shared" ref="A5:A68" si="9">A4+1</f>
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <f t="shared" ref="B5:B12" si="11">B4-500</f>
+        <f t="shared" ref="B5:B12" si="10">B4-500</f>
         <v>8500</v>
       </c>
       <c r="C5" s="1">
-        <f t="shared" ref="C5:C12" si="12">C4+500</f>
+        <f t="shared" ref="C5:C12" si="11">C4+500</f>
         <v>1500</v>
       </c>
       <c r="D5" s="4">
         <v>0</v>
       </c>
       <c r="E5" s="4">
-        <f t="shared" ref="E5:E42" si="13">E4+1</f>
+        <f t="shared" ref="E5:E42" si="12">E4+1</f>
         <v>3</v>
       </c>
       <c r="F5" s="13">
-        <f t="shared" ref="F5:F21" si="14">F4+0.005</f>
-        <v>0.02</v>
+        <f t="shared" ref="F5:F22" si="13">F4+0.01</f>
+        <v>0.22000000000000003</v>
       </c>
       <c r="G5" s="12">
-        <f t="shared" si="5"/>
-        <v>156</v>
+        <f t="shared" ref="G5:G68" si="14">150+ROUNDUP(A5*3.5,0)+ROUNDUP(G4/3,0)</f>
+        <v>231</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J5" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.85</v>
       </c>
       <c r="K5" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="L5" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M5" s="4">
-        <f t="shared" si="9"/>
-        <v>156</v>
+        <f t="shared" si="8"/>
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
         <f t="shared" si="10"/>
-        <v>4</v>
-      </c>
-      <c r="B6" s="1">
+        <v>8000</v>
+      </c>
+      <c r="C6" s="1">
         <f t="shared" si="11"/>
-        <v>8000</v>
-      </c>
-      <c r="C6" s="1">
-        <f t="shared" si="12"/>
         <v>2000</v>
       </c>
       <c r="D6" s="4">
         <v>0</v>
       </c>
       <c r="E6" s="4">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="F6" s="13">
         <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="F6" s="13">
-        <f t="shared" si="14"/>
-        <v>2.5000000000000001E-2</v>
+        <v>0.23000000000000004</v>
       </c>
       <c r="G6" s="12">
-        <f t="shared" si="5"/>
-        <v>158</v>
+        <f t="shared" si="14"/>
+        <v>241</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J6" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
       <c r="K6" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
       <c r="L6" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M6" s="4">
-        <f t="shared" si="9"/>
-        <v>158</v>
+        <f t="shared" si="8"/>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
         <f t="shared" si="10"/>
-        <v>5</v>
-      </c>
-      <c r="B7" s="1">
+        <v>7500</v>
+      </c>
+      <c r="C7" s="1">
         <f t="shared" si="11"/>
-        <v>7500</v>
-      </c>
-      <c r="C7" s="1">
-        <f t="shared" si="12"/>
         <v>2500</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
       </c>
       <c r="E7" s="4">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="F7" s="13">
         <f t="shared" si="13"/>
-        <v>5</v>
-      </c>
-      <c r="F7" s="13">
-        <f t="shared" si="14"/>
-        <v>3.0000000000000002E-2</v>
+        <v>0.24000000000000005</v>
       </c>
       <c r="G7" s="12">
-        <f t="shared" si="5"/>
-        <v>160</v>
+        <f t="shared" si="14"/>
+        <v>249</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J7" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.75</v>
       </c>
       <c r="K7" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="L7" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M7" s="4">
-        <f t="shared" si="9"/>
-        <v>160</v>
+        <f t="shared" si="8"/>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
+        <f t="shared" si="9"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
         <f t="shared" si="10"/>
-        <v>6</v>
-      </c>
-      <c r="B8" s="1">
+        <v>7000</v>
+      </c>
+      <c r="C8" s="1">
         <f t="shared" si="11"/>
-        <v>7000</v>
-      </c>
-      <c r="C8" s="1">
-        <f t="shared" si="12"/>
         <v>3000</v>
       </c>
       <c r="D8" s="4">
         <v>0</v>
       </c>
       <c r="E8" s="4">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="F8" s="13">
         <f t="shared" si="13"/>
-        <v>6</v>
-      </c>
-      <c r="F8" s="13">
-        <f t="shared" si="14"/>
-        <v>3.5000000000000003E-2</v>
+        <v>0.25000000000000006</v>
       </c>
       <c r="G8" s="12">
-        <f t="shared" si="5"/>
-        <v>162</v>
+        <f t="shared" si="14"/>
+        <v>254</v>
       </c>
       <c r="I8" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J8" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
       <c r="K8" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="L8" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M8" s="4">
-        <f t="shared" si="9"/>
-        <v>162</v>
+        <f t="shared" si="8"/>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="1">
         <f t="shared" si="10"/>
-        <v>7</v>
-      </c>
-      <c r="B9" s="1">
+        <v>6500</v>
+      </c>
+      <c r="C9" s="1">
         <f t="shared" si="11"/>
-        <v>6500</v>
-      </c>
-      <c r="C9" s="1">
-        <f t="shared" si="12"/>
         <v>3500</v>
       </c>
       <c r="D9" s="4">
         <v>0</v>
       </c>
       <c r="E9" s="4">
+        <f t="shared" si="12"/>
+        <v>7</v>
+      </c>
+      <c r="F9" s="13">
         <f t="shared" si="13"/>
-        <v>7</v>
-      </c>
-      <c r="F9" s="13">
-        <f t="shared" si="14"/>
-        <v>0.04</v>
+        <v>0.26000000000000006</v>
       </c>
       <c r="G9" s="12">
-        <f t="shared" si="5"/>
-        <v>164</v>
+        <f t="shared" si="14"/>
+        <v>260</v>
       </c>
       <c r="I9" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.65</v>
       </c>
       <c r="K9" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.35</v>
       </c>
       <c r="L9" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M9" s="4">
-        <f t="shared" si="9"/>
-        <v>164</v>
+        <f t="shared" si="8"/>
+        <v>260</v>
       </c>
     </row>
     <row r="10" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
         <f t="shared" si="10"/>
-        <v>8</v>
-      </c>
-      <c r="B10" s="1">
+        <v>6000</v>
+      </c>
+      <c r="C10" s="1">
         <f t="shared" si="11"/>
-        <v>6000</v>
-      </c>
-      <c r="C10" s="1">
-        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="D10" s="4">
         <v>0</v>
       </c>
       <c r="E10" s="4">
+        <f t="shared" si="12"/>
+        <v>8</v>
+      </c>
+      <c r="F10" s="13">
         <f t="shared" si="13"/>
-        <v>8</v>
-      </c>
-      <c r="F10" s="13">
-        <f t="shared" si="14"/>
-        <v>4.4999999999999998E-2</v>
+        <v>0.27000000000000007</v>
       </c>
       <c r="G10" s="12">
-        <f t="shared" si="5"/>
-        <v>166</v>
+        <f t="shared" si="14"/>
+        <v>265</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J10" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.6</v>
       </c>
       <c r="K10" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.4</v>
       </c>
       <c r="L10" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M10" s="4">
-        <f t="shared" si="9"/>
-        <v>166</v>
+        <f t="shared" si="8"/>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="B11" s="1">
         <f t="shared" si="10"/>
-        <v>9</v>
-      </c>
-      <c r="B11" s="1">
+        <v>5500</v>
+      </c>
+      <c r="C11" s="1">
         <f t="shared" si="11"/>
-        <v>5500</v>
-      </c>
-      <c r="C11" s="1">
-        <f t="shared" si="12"/>
         <v>4500</v>
       </c>
       <c r="D11" s="4">
         <v>0</v>
       </c>
       <c r="E11" s="4">
+        <f t="shared" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="F11" s="13">
         <f t="shared" si="13"/>
-        <v>9</v>
-      </c>
-      <c r="F11" s="13">
-        <f t="shared" si="14"/>
-        <v>4.9999999999999996E-2</v>
+        <v>0.28000000000000008</v>
       </c>
       <c r="G11" s="12">
-        <f t="shared" si="5"/>
-        <v>168</v>
+        <f t="shared" si="14"/>
+        <v>271</v>
       </c>
       <c r="I11" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J11" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="K11" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.45</v>
       </c>
       <c r="L11" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M11" s="4">
-        <f t="shared" si="9"/>
-        <v>168</v>
+        <f t="shared" si="8"/>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+      <c r="B12" s="1">
         <f t="shared" si="10"/>
-        <v>10</v>
-      </c>
-      <c r="B12" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C12" s="1">
         <f t="shared" si="11"/>
         <v>5000</v>
       </c>
-      <c r="C12" s="1">
-        <f t="shared" si="12"/>
-        <v>5000</v>
-      </c>
       <c r="D12" s="4">
         <v>0</v>
       </c>
       <c r="E12" s="4">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="F12" s="13">
         <f t="shared" si="13"/>
-        <v>10</v>
-      </c>
-      <c r="F12" s="13">
-        <f t="shared" si="14"/>
-        <v>5.4999999999999993E-2</v>
+        <v>0.29000000000000009</v>
       </c>
       <c r="G12" s="12">
-        <f t="shared" si="5"/>
-        <v>170</v>
+        <f t="shared" si="14"/>
+        <v>276</v>
       </c>
       <c r="I12" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J12" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
       <c r="K12" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="L12" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M12" s="4">
-        <f t="shared" si="9"/>
-        <v>170</v>
+        <f t="shared" si="8"/>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="B13" s="1">
@@ -1100,41 +1100,41 @@
         <v>0</v>
       </c>
       <c r="E13" s="4">
+        <f t="shared" si="12"/>
+        <v>11</v>
+      </c>
+      <c r="F13" s="13">
         <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="F13" s="13">
-        <f t="shared" si="14"/>
-        <v>5.9999999999999991E-2</v>
+        <v>0.3000000000000001</v>
       </c>
       <c r="G13" s="12">
-        <f t="shared" si="5"/>
-        <v>172</v>
+        <f t="shared" si="14"/>
+        <v>281</v>
       </c>
       <c r="I13" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J13" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.48</v>
       </c>
       <c r="K13" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.52</v>
       </c>
       <c r="L13" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M13" s="4">
-        <f t="shared" si="9"/>
-        <v>172</v>
+        <f t="shared" si="8"/>
+        <v>281</v>
       </c>
     </row>
     <row r="14" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="B14" s="1">
@@ -1149,41 +1149,41 @@
         <v>0</v>
       </c>
       <c r="E14" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
       <c r="F14" s="13">
-        <f t="shared" si="14"/>
-        <v>6.4999999999999988E-2</v>
+        <f>F13+0.008</f>
+        <v>0.30800000000000011</v>
       </c>
       <c r="G14" s="12">
-        <f t="shared" si="5"/>
-        <v>174</v>
+        <f t="shared" si="14"/>
+        <v>286</v>
       </c>
       <c r="I14" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.46</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.54</v>
       </c>
       <c r="L14" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M14" s="4">
-        <f t="shared" si="9"/>
-        <v>174</v>
+        <f t="shared" si="8"/>
+        <v>286</v>
       </c>
     </row>
     <row r="15" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
       <c r="B15" s="1">
@@ -1198,41 +1198,41 @@
         <v>0</v>
       </c>
       <c r="E15" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="14"/>
-        <v>6.9999999999999993E-2</v>
+        <f t="shared" ref="F15:F42" si="17">F14+0.008</f>
+        <v>0.31600000000000011</v>
       </c>
       <c r="G15" s="12">
-        <f t="shared" si="5"/>
-        <v>176</v>
+        <f t="shared" si="14"/>
+        <v>292</v>
       </c>
       <c r="I15" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J15" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.44</v>
       </c>
       <c r="K15" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="L15" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M15" s="4">
-        <f t="shared" si="9"/>
-        <v>176</v>
+        <f t="shared" si="8"/>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="B16" s="1">
@@ -1247,41 +1247,41 @@
         <v>0</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="F16" s="13">
-        <f t="shared" si="14"/>
-        <v>7.4999999999999997E-2</v>
+        <f t="shared" si="17"/>
+        <v>0.32400000000000012</v>
       </c>
       <c r="G16" s="12">
-        <f t="shared" si="5"/>
-        <v>178</v>
+        <f t="shared" si="14"/>
+        <v>297</v>
       </c>
       <c r="I16" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J16" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.42</v>
       </c>
       <c r="K16" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="L16" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M16" s="4">
-        <f t="shared" si="9"/>
-        <v>178</v>
+        <f t="shared" si="8"/>
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
       <c r="B17" s="1">
@@ -1296,41 +1296,41 @@
         <v>0</v>
       </c>
       <c r="E17" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="F17" s="13">
-        <f t="shared" si="14"/>
-        <v>0.08</v>
+        <f t="shared" si="17"/>
+        <v>0.33200000000000013</v>
       </c>
       <c r="G17" s="12">
-        <f t="shared" si="5"/>
-        <v>180</v>
+        <f t="shared" si="14"/>
+        <v>302</v>
       </c>
       <c r="I17" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J17" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.4</v>
       </c>
       <c r="K17" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
       <c r="L17" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M17" s="4">
-        <f t="shared" si="9"/>
-        <v>180</v>
+        <f t="shared" si="8"/>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="B18" s="1">
@@ -1345,41 +1345,41 @@
         <v>0</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>16</v>
       </c>
       <c r="F18" s="13">
-        <f t="shared" si="14"/>
-        <v>8.5000000000000006E-2</v>
+        <f t="shared" si="17"/>
+        <v>0.34000000000000014</v>
       </c>
       <c r="G18" s="12">
-        <f t="shared" si="5"/>
-        <v>182</v>
+        <f t="shared" si="14"/>
+        <v>307</v>
       </c>
       <c r="I18" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J18" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.38</v>
       </c>
       <c r="K18" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.62</v>
       </c>
       <c r="L18" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M18" s="4">
-        <f t="shared" si="9"/>
-        <v>182</v>
+        <f t="shared" si="8"/>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
       <c r="B19" s="1">
@@ -1394,41 +1394,41 @@
         <v>0</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>17</v>
       </c>
       <c r="F19" s="13">
-        <f t="shared" si="14"/>
-        <v>9.0000000000000011E-2</v>
+        <f t="shared" si="17"/>
+        <v>0.34800000000000014</v>
       </c>
       <c r="G19" s="12">
-        <f t="shared" si="5"/>
-        <v>184</v>
+        <f t="shared" si="14"/>
+        <v>313</v>
       </c>
       <c r="I19" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J19" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.36</v>
       </c>
       <c r="K19" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.64</v>
       </c>
       <c r="L19" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M19" s="4">
-        <f t="shared" si="9"/>
-        <v>184</v>
+        <f t="shared" si="8"/>
+        <v>313</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="B20" s="1">
@@ -1443,41 +1443,41 @@
         <v>0</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>18</v>
       </c>
       <c r="F20" s="13">
-        <f t="shared" si="14"/>
-        <v>9.5000000000000015E-2</v>
+        <f t="shared" si="17"/>
+        <v>0.35600000000000015</v>
       </c>
       <c r="G20" s="12">
-        <f t="shared" si="5"/>
-        <v>186</v>
+        <f t="shared" si="14"/>
+        <v>318</v>
       </c>
       <c r="I20" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J20" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.34</v>
       </c>
       <c r="K20" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.66</v>
       </c>
       <c r="L20" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M20" s="4">
-        <f t="shared" si="9"/>
-        <v>186</v>
+        <f t="shared" si="8"/>
+        <v>318</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>19</v>
       </c>
       <c r="B21" s="1">
@@ -1492,41 +1492,41 @@
         <v>0</v>
       </c>
       <c r="E21" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>19</v>
       </c>
       <c r="F21" s="13">
-        <f t="shared" si="14"/>
-        <v>0.10000000000000002</v>
+        <f t="shared" si="17"/>
+        <v>0.36400000000000016</v>
       </c>
       <c r="G21" s="12">
-        <f t="shared" si="5"/>
-        <v>188</v>
+        <f t="shared" si="14"/>
+        <v>323</v>
       </c>
       <c r="I21" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J21" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.32</v>
       </c>
       <c r="K21" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.68</v>
       </c>
       <c r="L21" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M21" s="4">
-        <f t="shared" si="9"/>
-        <v>188</v>
+        <f t="shared" si="8"/>
+        <v>323</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="B22" s="1">
@@ -1541,41 +1541,41 @@
         <v>0</v>
       </c>
       <c r="E22" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="F22" s="13">
-        <f>F21+0.008</f>
-        <v>0.10800000000000001</v>
+        <f t="shared" si="17"/>
+        <v>0.37200000000000016</v>
       </c>
       <c r="G22" s="12">
-        <f t="shared" si="5"/>
-        <v>190</v>
+        <f t="shared" si="14"/>
+        <v>328</v>
       </c>
       <c r="I22" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J22" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K22" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.7</v>
       </c>
       <c r="L22" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M22" s="4">
-        <f t="shared" si="9"/>
-        <v>190</v>
+        <f t="shared" si="8"/>
+        <v>328</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="B23" s="1">
@@ -1590,41 +1590,41 @@
         <v>20</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>21</v>
       </c>
       <c r="F23" s="13">
-        <f t="shared" ref="F23:F41" si="17">F22+0.008</f>
-        <v>0.11600000000000002</v>
+        <f t="shared" si="17"/>
+        <v>0.38000000000000017</v>
       </c>
       <c r="G23" s="12">
-        <f t="shared" si="5"/>
-        <v>192</v>
+        <f t="shared" si="14"/>
+        <v>334</v>
       </c>
       <c r="I23" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J23" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K23" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.69799999999999995</v>
       </c>
       <c r="L23" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2E-3</v>
       </c>
       <c r="M23" s="4">
-        <f t="shared" si="9"/>
-        <v>192</v>
+        <f t="shared" si="8"/>
+        <v>334</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>22</v>
       </c>
       <c r="B24" s="1">
@@ -1639,41 +1639,41 @@
         <v>40</v>
       </c>
       <c r="E24" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>22</v>
       </c>
       <c r="F24" s="13">
         <f t="shared" si="17"/>
-        <v>0.12400000000000003</v>
+        <v>0.38800000000000018</v>
       </c>
       <c r="G24" s="12">
-        <f t="shared" si="5"/>
-        <v>194</v>
+        <f t="shared" si="14"/>
+        <v>339</v>
       </c>
       <c r="I24" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J24" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K24" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.69599999999999995</v>
       </c>
       <c r="L24" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="M24" s="4">
-        <f t="shared" si="9"/>
-        <v>194</v>
+        <f t="shared" si="8"/>
+        <v>339</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>23</v>
       </c>
       <c r="B25" s="1">
@@ -1688,41 +1688,41 @@
         <v>60</v>
       </c>
       <c r="E25" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
       <c r="F25" s="13">
         <f t="shared" si="17"/>
-        <v>0.13200000000000003</v>
+        <v>0.39600000000000019</v>
       </c>
       <c r="G25" s="12">
-        <f t="shared" si="5"/>
-        <v>196</v>
+        <f t="shared" si="14"/>
+        <v>344</v>
       </c>
       <c r="I25" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J25" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K25" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.69399999999999995</v>
       </c>
       <c r="L25" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="M25" s="4">
-        <f t="shared" si="9"/>
-        <v>196</v>
+        <f t="shared" si="8"/>
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>24</v>
       </c>
       <c r="B26" s="1">
@@ -1737,41 +1737,41 @@
         <v>80</v>
       </c>
       <c r="E26" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="F26" s="13">
         <f t="shared" si="17"/>
-        <v>0.14000000000000004</v>
+        <v>0.40400000000000019</v>
       </c>
       <c r="G26" s="12">
-        <f t="shared" si="5"/>
-        <v>198</v>
+        <f t="shared" si="14"/>
+        <v>349</v>
       </c>
       <c r="I26" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J26" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K26" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.69199999999999995</v>
       </c>
       <c r="L26" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="M26" s="4">
-        <f t="shared" si="9"/>
-        <v>198</v>
+        <f t="shared" si="8"/>
+        <v>349</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>25</v>
       </c>
       <c r="B27" s="1">
@@ -1786,41 +1786,41 @@
         <v>100</v>
       </c>
       <c r="E27" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>25</v>
       </c>
       <c r="F27" s="13">
         <f t="shared" si="17"/>
-        <v>0.14800000000000005</v>
+        <v>0.4120000000000002</v>
       </c>
       <c r="G27" s="12">
-        <f t="shared" si="5"/>
-        <v>200</v>
+        <f t="shared" si="14"/>
+        <v>355</v>
       </c>
       <c r="I27" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J27" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K27" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.69</v>
       </c>
       <c r="L27" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.01</v>
       </c>
       <c r="M27" s="4">
-        <f t="shared" si="9"/>
-        <v>200</v>
+        <f t="shared" si="8"/>
+        <v>355</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>26</v>
       </c>
       <c r="B28" s="1">
@@ -1835,41 +1835,41 @@
         <v>120</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>26</v>
       </c>
       <c r="F28" s="13">
         <f t="shared" si="17"/>
-        <v>0.15600000000000006</v>
+        <v>0.42000000000000021</v>
       </c>
       <c r="G28" s="12">
-        <f t="shared" si="5"/>
-        <v>202</v>
+        <f t="shared" si="14"/>
+        <v>360</v>
       </c>
       <c r="I28" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J28" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K28" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.68799999999999994</v>
       </c>
       <c r="L28" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.2E-2</v>
       </c>
       <c r="M28" s="4">
-        <f t="shared" si="9"/>
-        <v>202</v>
+        <f t="shared" si="8"/>
+        <v>360</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>27</v>
       </c>
       <c r="B29" s="1">
@@ -1884,41 +1884,41 @@
         <v>140</v>
       </c>
       <c r="E29" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>27</v>
       </c>
       <c r="F29" s="13">
         <f t="shared" si="17"/>
-        <v>0.16400000000000006</v>
+        <v>0.42800000000000021</v>
       </c>
       <c r="G29" s="12">
-        <f t="shared" si="5"/>
-        <v>204</v>
+        <f t="shared" si="14"/>
+        <v>365</v>
       </c>
       <c r="I29" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J29" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K29" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.68600000000000005</v>
       </c>
       <c r="L29" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.4E-2</v>
       </c>
       <c r="M29" s="4">
-        <f t="shared" si="9"/>
-        <v>204</v>
+        <f t="shared" si="8"/>
+        <v>365</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="B30" s="1">
@@ -1933,41 +1933,41 @@
         <v>160</v>
       </c>
       <c r="E30" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>28</v>
       </c>
       <c r="F30" s="13">
         <f t="shared" si="17"/>
-        <v>0.17200000000000007</v>
+        <v>0.43600000000000022</v>
       </c>
       <c r="G30" s="12">
-        <f t="shared" si="5"/>
-        <v>206</v>
+        <f t="shared" si="14"/>
+        <v>370</v>
       </c>
       <c r="I30" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J30" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K30" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.68400000000000005</v>
       </c>
       <c r="L30" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.6E-2</v>
       </c>
       <c r="M30" s="4">
-        <f t="shared" si="9"/>
-        <v>206</v>
+        <f t="shared" si="8"/>
+        <v>370</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>29</v>
       </c>
       <c r="B31" s="1">
@@ -1982,41 +1982,41 @@
         <v>180</v>
       </c>
       <c r="E31" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>29</v>
       </c>
       <c r="F31" s="13">
         <f t="shared" si="17"/>
-        <v>0.18000000000000008</v>
+        <v>0.44400000000000023</v>
       </c>
       <c r="G31" s="12">
-        <f t="shared" si="5"/>
-        <v>208</v>
+        <f t="shared" si="14"/>
+        <v>376</v>
       </c>
       <c r="I31" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J31" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K31" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.68200000000000005</v>
       </c>
       <c r="L31" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="M31" s="4">
-        <f t="shared" si="9"/>
-        <v>208</v>
+        <f t="shared" si="8"/>
+        <v>376</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="B32" s="1">
@@ -2031,41 +2031,41 @@
         <v>200</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="F32" s="13">
         <f t="shared" si="17"/>
-        <v>0.18800000000000008</v>
+        <v>0.45200000000000023</v>
       </c>
       <c r="G32" s="12">
-        <f t="shared" si="5"/>
-        <v>210</v>
+        <f t="shared" si="14"/>
+        <v>381</v>
       </c>
       <c r="I32" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J32" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K32" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.68</v>
       </c>
       <c r="L32" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.02</v>
       </c>
       <c r="M32" s="4">
-        <f t="shared" si="9"/>
-        <v>210</v>
+        <f t="shared" si="8"/>
+        <v>381</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>31</v>
       </c>
       <c r="B33" s="1">
@@ -2080,41 +2080,41 @@
         <v>220</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="F33" s="13">
         <f t="shared" si="17"/>
-        <v>0.19600000000000009</v>
+        <v>0.46000000000000024</v>
       </c>
       <c r="G33" s="12">
-        <f t="shared" si="5"/>
-        <v>212</v>
+        <f t="shared" si="14"/>
+        <v>386</v>
       </c>
       <c r="I33" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J33" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K33" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.67800000000000005</v>
       </c>
       <c r="L33" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="M33" s="4">
-        <f t="shared" si="9"/>
-        <v>212</v>
+        <f t="shared" si="8"/>
+        <v>386</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>32</v>
       </c>
       <c r="B34" s="1">
@@ -2129,41 +2129,41 @@
         <v>240</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>32</v>
       </c>
       <c r="F34" s="13">
         <f t="shared" si="17"/>
-        <v>0.2040000000000001</v>
+        <v>0.46800000000000025</v>
       </c>
       <c r="G34" s="12">
-        <f t="shared" si="5"/>
-        <v>214</v>
+        <f t="shared" si="14"/>
+        <v>391</v>
       </c>
       <c r="I34" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J34" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K34" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.67600000000000005</v>
       </c>
       <c r="L34" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2.4E-2</v>
       </c>
       <c r="M34" s="4">
-        <f t="shared" si="9"/>
-        <v>214</v>
+        <f t="shared" si="8"/>
+        <v>391</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>33</v>
       </c>
       <c r="B35" s="1">
@@ -2178,41 +2178,41 @@
         <v>260</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>33</v>
       </c>
       <c r="F35" s="13">
         <f t="shared" si="17"/>
-        <v>0.21200000000000011</v>
+        <v>0.47600000000000026</v>
       </c>
       <c r="G35" s="12">
-        <f t="shared" si="5"/>
-        <v>216</v>
+        <f t="shared" si="14"/>
+        <v>397</v>
       </c>
       <c r="I35" s="4">
         <f t="shared" ref="I35:I66" si="20">SUM(B35:D35)</f>
         <v>10000</v>
       </c>
       <c r="J35" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K35" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.67400000000000004</v>
       </c>
       <c r="L35" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="M35" s="4">
-        <f t="shared" si="9"/>
-        <v>216</v>
+        <f t="shared" si="8"/>
+        <v>397</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>34</v>
       </c>
       <c r="B36" s="1">
@@ -2227,41 +2227,41 @@
         <v>280</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>34</v>
       </c>
       <c r="F36" s="13">
         <f t="shared" si="17"/>
-        <v>0.22000000000000011</v>
+        <v>0.48400000000000026</v>
       </c>
       <c r="G36" s="12">
-        <f t="shared" si="5"/>
-        <v>218</v>
+        <f t="shared" si="14"/>
+        <v>402</v>
       </c>
       <c r="I36" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J36" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K36" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.67200000000000004</v>
       </c>
       <c r="L36" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="M36" s="4">
-        <f t="shared" si="9"/>
-        <v>218</v>
+        <f t="shared" si="8"/>
+        <v>402</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>35</v>
       </c>
       <c r="B37" s="1">
@@ -2276,41 +2276,41 @@
         <v>300</v>
       </c>
       <c r="E37" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>35</v>
       </c>
       <c r="F37" s="13">
         <f t="shared" si="17"/>
-        <v>0.22800000000000012</v>
+        <v>0.49200000000000027</v>
       </c>
       <c r="G37" s="12">
-        <f t="shared" si="5"/>
-        <v>220</v>
+        <f t="shared" si="14"/>
+        <v>407</v>
       </c>
       <c r="I37" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J37" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K37" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.67</v>
       </c>
       <c r="L37" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.03</v>
       </c>
       <c r="M37" s="4">
-        <f t="shared" si="9"/>
-        <v>220</v>
+        <f t="shared" si="8"/>
+        <v>407</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>36</v>
       </c>
       <c r="B38" s="1">
@@ -2325,41 +2325,41 @@
         <v>320</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>36</v>
       </c>
       <c r="F38" s="13">
         <f t="shared" si="17"/>
-        <v>0.23600000000000013</v>
+        <v>0.50000000000000022</v>
       </c>
       <c r="G38" s="12">
-        <f t="shared" si="5"/>
-        <v>222</v>
+        <f t="shared" si="14"/>
+        <v>412</v>
       </c>
       <c r="I38" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J38" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K38" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.66800000000000004</v>
       </c>
       <c r="L38" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="M38" s="4">
-        <f t="shared" si="9"/>
-        <v>222</v>
+        <f t="shared" si="8"/>
+        <v>412</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>37</v>
       </c>
       <c r="B39" s="1">
@@ -2374,41 +2374,41 @@
         <v>340</v>
       </c>
       <c r="E39" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>37</v>
       </c>
       <c r="F39" s="13">
         <f t="shared" si="17"/>
-        <v>0.24400000000000013</v>
+        <v>0.50800000000000023</v>
       </c>
       <c r="G39" s="12">
-        <f t="shared" si="5"/>
-        <v>224</v>
+        <f t="shared" si="14"/>
+        <v>418</v>
       </c>
       <c r="I39" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J39" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K39" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.66600000000000004</v>
       </c>
       <c r="L39" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="M39" s="4">
-        <f t="shared" si="9"/>
-        <v>224</v>
+        <f t="shared" si="8"/>
+        <v>418</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>38</v>
       </c>
       <c r="B40" s="1">
@@ -2423,41 +2423,41 @@
         <v>360</v>
       </c>
       <c r="E40" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>38</v>
       </c>
       <c r="F40" s="13">
         <f t="shared" si="17"/>
-        <v>0.25200000000000011</v>
+        <v>0.51600000000000024</v>
       </c>
       <c r="G40" s="12">
-        <f t="shared" si="5"/>
-        <v>226</v>
+        <f t="shared" si="14"/>
+        <v>423</v>
       </c>
       <c r="I40" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J40" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K40" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.66400000000000003</v>
       </c>
       <c r="L40" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="M40" s="4">
-        <f t="shared" si="9"/>
-        <v>226</v>
+        <f t="shared" si="8"/>
+        <v>423</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>39</v>
       </c>
       <c r="B41" s="1">
@@ -2472,41 +2472,41 @@
         <v>380</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>39</v>
       </c>
       <c r="F41" s="13">
         <f t="shared" si="17"/>
-        <v>0.26000000000000012</v>
+        <v>0.52400000000000024</v>
       </c>
       <c r="G41" s="12">
-        <f t="shared" si="5"/>
-        <v>228</v>
+        <f t="shared" si="14"/>
+        <v>428</v>
       </c>
       <c r="I41" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J41" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="K41" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.66200000000000003</v>
       </c>
       <c r="L41" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="M41" s="4">
-        <f t="shared" si="9"/>
-        <v>228</v>
+        <f t="shared" si="8"/>
+        <v>428</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="B42" s="1">
@@ -2519,41 +2519,41 @@
         <v>0</v>
       </c>
       <c r="E42" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>40</v>
       </c>
       <c r="F42" s="13">
-        <f>F41+0.013</f>
-        <v>0.27300000000000013</v>
+        <f t="shared" si="17"/>
+        <v>0.53200000000000025</v>
       </c>
       <c r="G42" s="12">
-        <f>200+A42*3</f>
-        <v>320</v>
+        <f t="shared" si="14"/>
+        <v>433</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J42" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K42" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
       <c r="L42" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M42" s="4">
-        <f t="shared" si="9"/>
-        <v>320</v>
+        <f t="shared" si="8"/>
+        <v>433</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>41</v>
       </c>
       <c r="B43" s="1">
@@ -2572,37 +2572,37 @@
         <v>42</v>
       </c>
       <c r="F43" s="13">
-        <f t="shared" ref="F43:F61" si="21">F42+0.013</f>
-        <v>0.28600000000000014</v>
+        <f>F42+0.006</f>
+        <v>0.53800000000000026</v>
       </c>
       <c r="G43" s="12">
-        <f t="shared" ref="G43:G61" si="22">200+A43*3</f>
-        <v>323</v>
+        <f t="shared" si="14"/>
+        <v>439</v>
       </c>
       <c r="I43" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J43" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K43" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.745</v>
       </c>
       <c r="L43" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="M43" s="4">
-        <f t="shared" si="9"/>
-        <v>323</v>
+        <f t="shared" si="8"/>
+        <v>439</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>42</v>
       </c>
       <c r="B44" s="1">
@@ -2613,878 +2613,878 @@
         <v>7400</v>
       </c>
       <c r="D44" s="4">
-        <f t="shared" ref="D44:D61" si="23">D43+50</f>
+        <f t="shared" ref="D44:D61" si="21">D43+50</f>
         <v>100</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" ref="E44:E61" si="24">E43+2</f>
+        <f t="shared" ref="E44:E61" si="22">E43+2</f>
         <v>44</v>
       </c>
       <c r="F44" s="13">
-        <f t="shared" si="21"/>
-        <v>0.29900000000000015</v>
+        <f t="shared" ref="F44:F64" si="23">F43+0.006</f>
+        <v>0.54400000000000026</v>
       </c>
       <c r="G44" s="12">
-        <f t="shared" si="22"/>
-        <v>326</v>
+        <f t="shared" si="14"/>
+        <v>444</v>
       </c>
       <c r="I44" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J44" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K44" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.74</v>
       </c>
       <c r="L44" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.01</v>
       </c>
       <c r="M44" s="4">
-        <f t="shared" si="9"/>
-        <v>326</v>
+        <f t="shared" si="8"/>
+        <v>444</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>43</v>
       </c>
       <c r="B45" s="1">
         <v>2500</v>
       </c>
       <c r="C45" s="1">
-        <f t="shared" ref="C45:C61" si="25">$C$42-D45</f>
+        <f t="shared" ref="C45:C61" si="24">$C$42-D45</f>
         <v>7350</v>
       </c>
       <c r="D45" s="4">
+        <f t="shared" si="21"/>
+        <v>150</v>
+      </c>
+      <c r="E45" s="4">
+        <f t="shared" si="22"/>
+        <v>46</v>
+      </c>
+      <c r="F45" s="13">
         <f t="shared" si="23"/>
-        <v>150</v>
-      </c>
-      <c r="E45" s="4">
-        <f t="shared" si="24"/>
-        <v>46</v>
-      </c>
-      <c r="F45" s="13">
-        <f t="shared" si="21"/>
-        <v>0.31200000000000017</v>
+        <v>0.55000000000000027</v>
       </c>
       <c r="G45" s="12">
-        <f t="shared" si="22"/>
-        <v>329</v>
+        <f t="shared" si="14"/>
+        <v>449</v>
       </c>
       <c r="I45" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J45" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K45" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.73499999999999999</v>
       </c>
       <c r="L45" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="M45" s="4">
-        <f t="shared" si="9"/>
-        <v>329</v>
+        <f t="shared" si="8"/>
+        <v>449</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>44</v>
       </c>
       <c r="B46" s="1">
         <v>2500</v>
       </c>
       <c r="C46" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>7300</v>
       </c>
       <c r="D46" s="4">
+        <f t="shared" si="21"/>
+        <v>200</v>
+      </c>
+      <c r="E46" s="4">
+        <f t="shared" si="22"/>
+        <v>48</v>
+      </c>
+      <c r="F46" s="13">
         <f t="shared" si="23"/>
-        <v>200</v>
-      </c>
-      <c r="E46" s="4">
-        <f t="shared" si="24"/>
-        <v>48</v>
-      </c>
-      <c r="F46" s="13">
-        <f t="shared" si="21"/>
-        <v>0.32500000000000018</v>
+        <v>0.55600000000000027</v>
       </c>
       <c r="G46" s="12">
-        <f t="shared" si="22"/>
-        <v>332</v>
+        <f t="shared" si="14"/>
+        <v>454</v>
       </c>
       <c r="I46" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J46" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K46" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.73</v>
       </c>
       <c r="L46" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.02</v>
       </c>
       <c r="M46" s="4">
-        <f t="shared" si="9"/>
-        <v>332</v>
+        <f t="shared" si="8"/>
+        <v>454</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>45</v>
       </c>
       <c r="B47" s="1">
         <v>2500</v>
       </c>
       <c r="C47" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>7250</v>
       </c>
       <c r="D47" s="4">
+        <f t="shared" si="21"/>
+        <v>250</v>
+      </c>
+      <c r="E47" s="4">
+        <f t="shared" si="22"/>
+        <v>50</v>
+      </c>
+      <c r="F47" s="13">
         <f t="shared" si="23"/>
-        <v>250</v>
-      </c>
-      <c r="E47" s="4">
-        <f t="shared" si="24"/>
-        <v>50</v>
-      </c>
-      <c r="F47" s="13">
-        <f t="shared" si="21"/>
-        <v>0.33800000000000019</v>
+        <v>0.56200000000000028</v>
       </c>
       <c r="G47" s="12">
-        <f t="shared" si="22"/>
-        <v>335</v>
+        <f t="shared" si="14"/>
+        <v>460</v>
       </c>
       <c r="I47" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J47" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K47" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.72499999999999998</v>
       </c>
       <c r="L47" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M47" s="4">
-        <f t="shared" si="9"/>
-        <v>335</v>
+        <f t="shared" si="8"/>
+        <v>460</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>46</v>
       </c>
       <c r="B48" s="1">
         <v>2500</v>
       </c>
       <c r="C48" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>7200</v>
       </c>
       <c r="D48" s="4">
+        <f t="shared" si="21"/>
+        <v>300</v>
+      </c>
+      <c r="E48" s="4">
+        <f t="shared" si="22"/>
+        <v>52</v>
+      </c>
+      <c r="F48" s="13">
         <f t="shared" si="23"/>
-        <v>300</v>
-      </c>
-      <c r="E48" s="4">
-        <f t="shared" si="24"/>
-        <v>52</v>
-      </c>
-      <c r="F48" s="13">
-        <f t="shared" si="21"/>
-        <v>0.3510000000000002</v>
+        <v>0.56800000000000028</v>
       </c>
       <c r="G48" s="12">
-        <f t="shared" si="22"/>
-        <v>338</v>
+        <f t="shared" si="14"/>
+        <v>465</v>
       </c>
       <c r="I48" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J48" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K48" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.72</v>
       </c>
       <c r="L48" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.03</v>
       </c>
       <c r="M48" s="4">
-        <f t="shared" si="9"/>
-        <v>338</v>
+        <f t="shared" si="8"/>
+        <v>465</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>47</v>
       </c>
       <c r="B49" s="1">
         <v>2500</v>
       </c>
       <c r="C49" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>7150</v>
       </c>
       <c r="D49" s="4">
+        <f t="shared" si="21"/>
+        <v>350</v>
+      </c>
+      <c r="E49" s="4">
+        <f t="shared" si="22"/>
+        <v>54</v>
+      </c>
+      <c r="F49" s="13">
         <f t="shared" si="23"/>
-        <v>350</v>
-      </c>
-      <c r="E49" s="4">
-        <f t="shared" si="24"/>
-        <v>54</v>
-      </c>
-      <c r="F49" s="13">
-        <f t="shared" si="21"/>
-        <v>0.36400000000000021</v>
+        <v>0.57400000000000029</v>
       </c>
       <c r="G49" s="12">
-        <f t="shared" si="22"/>
-        <v>341</v>
+        <f t="shared" si="14"/>
+        <v>470</v>
       </c>
       <c r="I49" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J49" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K49" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.71499999999999997</v>
       </c>
       <c r="L49" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="M49" s="4">
-        <f t="shared" si="9"/>
-        <v>341</v>
+        <f t="shared" si="8"/>
+        <v>470</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>48</v>
       </c>
       <c r="B50" s="1">
         <v>2500</v>
       </c>
       <c r="C50" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>7100</v>
       </c>
       <c r="D50" s="4">
+        <f t="shared" si="21"/>
+        <v>400</v>
+      </c>
+      <c r="E50" s="4">
+        <f t="shared" si="22"/>
+        <v>56</v>
+      </c>
+      <c r="F50" s="13">
         <f t="shared" si="23"/>
-        <v>400</v>
-      </c>
-      <c r="E50" s="4">
-        <f t="shared" si="24"/>
-        <v>56</v>
-      </c>
-      <c r="F50" s="13">
-        <f t="shared" si="21"/>
-        <v>0.37700000000000022</v>
+        <v>0.58000000000000029</v>
       </c>
       <c r="G50" s="12">
-        <f t="shared" si="22"/>
-        <v>344</v>
+        <f t="shared" si="14"/>
+        <v>475</v>
       </c>
       <c r="I50" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J50" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K50" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.71</v>
       </c>
       <c r="L50" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
       <c r="M50" s="4">
-        <f t="shared" si="9"/>
-        <v>344</v>
+        <f t="shared" si="8"/>
+        <v>475</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>49</v>
       </c>
       <c r="B51" s="1">
         <v>2500</v>
       </c>
       <c r="C51" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>7050</v>
       </c>
       <c r="D51" s="4">
+        <f t="shared" si="21"/>
+        <v>450</v>
+      </c>
+      <c r="E51" s="4">
+        <f t="shared" si="22"/>
+        <v>58</v>
+      </c>
+      <c r="F51" s="13">
         <f t="shared" si="23"/>
-        <v>450</v>
-      </c>
-      <c r="E51" s="4">
-        <f t="shared" si="24"/>
-        <v>58</v>
-      </c>
-      <c r="F51" s="13">
-        <f t="shared" si="21"/>
-        <v>0.39000000000000024</v>
+        <v>0.5860000000000003</v>
       </c>
       <c r="G51" s="12">
-        <f t="shared" si="22"/>
-        <v>347</v>
+        <f t="shared" si="14"/>
+        <v>481</v>
       </c>
       <c r="I51" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J51" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K51" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.70499999999999996</v>
       </c>
       <c r="L51" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="M51" s="4">
-        <f t="shared" si="9"/>
-        <v>347</v>
+        <f t="shared" si="8"/>
+        <v>481</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>50</v>
       </c>
       <c r="B52" s="1">
         <v>2500</v>
       </c>
       <c r="C52" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>7000</v>
       </c>
       <c r="D52" s="4">
+        <f t="shared" si="21"/>
+        <v>500</v>
+      </c>
+      <c r="E52" s="4">
+        <f t="shared" si="22"/>
+        <v>60</v>
+      </c>
+      <c r="F52" s="13">
         <f t="shared" si="23"/>
-        <v>500</v>
-      </c>
-      <c r="E52" s="4">
-        <f t="shared" si="24"/>
-        <v>60</v>
-      </c>
-      <c r="F52" s="13">
-        <f t="shared" si="21"/>
-        <v>0.40300000000000025</v>
+        <v>0.5920000000000003</v>
       </c>
       <c r="G52" s="12">
-        <f t="shared" si="22"/>
-        <v>350</v>
+        <f t="shared" si="14"/>
+        <v>486</v>
       </c>
       <c r="I52" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J52" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K52" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.7</v>
       </c>
       <c r="L52" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
       <c r="M52" s="4">
-        <f t="shared" si="9"/>
-        <v>350</v>
+        <f t="shared" si="8"/>
+        <v>486</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>51</v>
       </c>
       <c r="B53" s="1">
         <v>2500</v>
       </c>
       <c r="C53" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>6950</v>
       </c>
       <c r="D53" s="4">
+        <f t="shared" si="21"/>
+        <v>550</v>
+      </c>
+      <c r="E53" s="4">
+        <f t="shared" si="22"/>
+        <v>62</v>
+      </c>
+      <c r="F53" s="13">
         <f t="shared" si="23"/>
-        <v>550</v>
-      </c>
-      <c r="E53" s="4">
-        <f t="shared" si="24"/>
-        <v>62</v>
-      </c>
-      <c r="F53" s="13">
-        <f t="shared" si="21"/>
-        <v>0.41600000000000026</v>
+        <v>0.59800000000000031</v>
       </c>
       <c r="G53" s="12">
-        <f t="shared" si="22"/>
-        <v>353</v>
+        <f t="shared" si="14"/>
+        <v>491</v>
       </c>
       <c r="I53" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J53" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K53" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.69499999999999995</v>
       </c>
       <c r="L53" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5.5E-2</v>
       </c>
       <c r="M53" s="4">
-        <f t="shared" si="9"/>
-        <v>353</v>
+        <f t="shared" si="8"/>
+        <v>491</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>52</v>
       </c>
       <c r="B54" s="1">
         <v>2500</v>
       </c>
       <c r="C54" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>6900</v>
       </c>
       <c r="D54" s="4">
+        <f t="shared" si="21"/>
+        <v>600</v>
+      </c>
+      <c r="E54" s="4">
+        <f t="shared" si="22"/>
+        <v>64</v>
+      </c>
+      <c r="F54" s="13">
         <f t="shared" si="23"/>
-        <v>600</v>
-      </c>
-      <c r="E54" s="4">
-        <f t="shared" si="24"/>
-        <v>64</v>
-      </c>
-      <c r="F54" s="13">
-        <f t="shared" si="21"/>
-        <v>0.42900000000000027</v>
+        <v>0.60400000000000031</v>
       </c>
       <c r="G54" s="12">
-        <f t="shared" si="22"/>
-        <v>356</v>
+        <f t="shared" si="14"/>
+        <v>496</v>
       </c>
       <c r="I54" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J54" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K54" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.69</v>
       </c>
       <c r="L54" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.06</v>
       </c>
       <c r="M54" s="4">
-        <f t="shared" si="9"/>
-        <v>356</v>
+        <f t="shared" si="8"/>
+        <v>496</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>53</v>
       </c>
       <c r="B55" s="1">
         <v>2500</v>
       </c>
       <c r="C55" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>6850</v>
       </c>
       <c r="D55" s="4">
+        <f t="shared" si="21"/>
+        <v>650</v>
+      </c>
+      <c r="E55" s="4">
+        <f t="shared" si="22"/>
+        <v>66</v>
+      </c>
+      <c r="F55" s="13">
         <f t="shared" si="23"/>
-        <v>650</v>
-      </c>
-      <c r="E55" s="4">
-        <f t="shared" si="24"/>
-        <v>66</v>
-      </c>
-      <c r="F55" s="13">
-        <f t="shared" si="21"/>
-        <v>0.44200000000000028</v>
+        <v>0.61000000000000032</v>
       </c>
       <c r="G55" s="12">
-        <f t="shared" si="22"/>
-        <v>359</v>
+        <f t="shared" si="14"/>
+        <v>502</v>
       </c>
       <c r="I55" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J55" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K55" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.68500000000000005</v>
       </c>
       <c r="L55" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="M55" s="4">
-        <f t="shared" si="9"/>
-        <v>359</v>
+        <f t="shared" si="8"/>
+        <v>502</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>54</v>
       </c>
       <c r="B56" s="1">
         <v>2500</v>
       </c>
       <c r="C56" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>6800</v>
       </c>
       <c r="D56" s="4">
+        <f t="shared" si="21"/>
+        <v>700</v>
+      </c>
+      <c r="E56" s="4">
+        <f t="shared" si="22"/>
+        <v>68</v>
+      </c>
+      <c r="F56" s="13">
         <f t="shared" si="23"/>
-        <v>700</v>
-      </c>
-      <c r="E56" s="4">
-        <f t="shared" si="24"/>
-        <v>68</v>
-      </c>
-      <c r="F56" s="13">
-        <f t="shared" si="21"/>
-        <v>0.45500000000000029</v>
+        <v>0.61600000000000033</v>
       </c>
       <c r="G56" s="12">
-        <f t="shared" si="22"/>
-        <v>362</v>
+        <f t="shared" si="14"/>
+        <v>507</v>
       </c>
       <c r="I56" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J56" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K56" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.68</v>
       </c>
       <c r="L56" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="M56" s="4">
-        <f t="shared" si="9"/>
-        <v>362</v>
+        <f t="shared" si="8"/>
+        <v>507</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>55</v>
       </c>
       <c r="B57" s="1">
         <v>2500</v>
       </c>
       <c r="C57" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>6750</v>
       </c>
       <c r="D57" s="4">
+        <f t="shared" si="21"/>
+        <v>750</v>
+      </c>
+      <c r="E57" s="4">
+        <f t="shared" si="22"/>
+        <v>70</v>
+      </c>
+      <c r="F57" s="13">
         <f t="shared" si="23"/>
-        <v>750</v>
-      </c>
-      <c r="E57" s="4">
-        <f t="shared" si="24"/>
-        <v>70</v>
-      </c>
-      <c r="F57" s="13">
-        <f t="shared" si="21"/>
-        <v>0.4680000000000003</v>
+        <v>0.62200000000000033</v>
       </c>
       <c r="G57" s="12">
-        <f t="shared" si="22"/>
-        <v>365</v>
+        <f t="shared" si="14"/>
+        <v>512</v>
       </c>
       <c r="I57" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J57" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K57" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.67500000000000004</v>
       </c>
       <c r="L57" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="M57" s="4">
-        <f t="shared" si="9"/>
-        <v>365</v>
+        <f t="shared" si="8"/>
+        <v>512</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>56</v>
       </c>
       <c r="B58" s="1">
         <v>2500</v>
       </c>
       <c r="C58" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>6700</v>
       </c>
       <c r="D58" s="4">
+        <f t="shared" si="21"/>
+        <v>800</v>
+      </c>
+      <c r="E58" s="4">
+        <f t="shared" si="22"/>
+        <v>72</v>
+      </c>
+      <c r="F58" s="13">
         <f t="shared" si="23"/>
-        <v>800</v>
-      </c>
-      <c r="E58" s="4">
-        <f t="shared" si="24"/>
-        <v>72</v>
-      </c>
-      <c r="F58" s="13">
-        <f t="shared" si="21"/>
-        <v>0.48100000000000032</v>
+        <v>0.62800000000000034</v>
       </c>
       <c r="G58" s="12">
-        <f t="shared" si="22"/>
-        <v>368</v>
+        <f t="shared" si="14"/>
+        <v>517</v>
       </c>
       <c r="I58" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J58" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.67</v>
       </c>
       <c r="L58" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
       <c r="M58" s="4">
-        <f t="shared" si="9"/>
-        <v>368</v>
+        <f t="shared" si="8"/>
+        <v>517</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>57</v>
       </c>
       <c r="B59" s="1">
         <v>2500</v>
       </c>
       <c r="C59" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>6650</v>
       </c>
       <c r="D59" s="4">
+        <f t="shared" si="21"/>
+        <v>850</v>
+      </c>
+      <c r="E59" s="4">
+        <f t="shared" si="22"/>
+        <v>74</v>
+      </c>
+      <c r="F59" s="13">
         <f t="shared" si="23"/>
-        <v>850</v>
-      </c>
-      <c r="E59" s="4">
-        <f t="shared" si="24"/>
-        <v>74</v>
-      </c>
-      <c r="F59" s="13">
-        <f t="shared" si="21"/>
-        <v>0.49400000000000033</v>
+        <v>0.63400000000000034</v>
       </c>
       <c r="G59" s="12">
-        <f t="shared" si="22"/>
-        <v>371</v>
+        <f t="shared" si="14"/>
+        <v>523</v>
       </c>
       <c r="I59" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J59" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K59" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.66500000000000004</v>
       </c>
       <c r="L59" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="M59" s="4">
-        <f t="shared" si="9"/>
-        <v>371</v>
+        <f t="shared" si="8"/>
+        <v>523</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>58</v>
       </c>
       <c r="B60" s="1">
         <v>2500</v>
       </c>
       <c r="C60" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>6600</v>
       </c>
       <c r="D60" s="4">
+        <f t="shared" si="21"/>
+        <v>900</v>
+      </c>
+      <c r="E60" s="4">
+        <f t="shared" si="22"/>
+        <v>76</v>
+      </c>
+      <c r="F60" s="13">
         <f t="shared" si="23"/>
-        <v>900</v>
-      </c>
-      <c r="E60" s="4">
-        <f t="shared" si="24"/>
-        <v>76</v>
-      </c>
-      <c r="F60" s="13">
-        <f t="shared" si="21"/>
-        <v>0.50700000000000034</v>
+        <v>0.64000000000000035</v>
       </c>
       <c r="G60" s="12">
-        <f t="shared" si="22"/>
-        <v>374</v>
+        <f t="shared" si="14"/>
+        <v>528</v>
       </c>
       <c r="I60" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J60" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K60" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.66</v>
       </c>
       <c r="L60" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
       <c r="M60" s="4">
-        <f t="shared" si="9"/>
-        <v>374</v>
+        <f t="shared" si="8"/>
+        <v>528</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>59</v>
       </c>
       <c r="B61" s="1">
         <v>2500</v>
       </c>
       <c r="C61" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>6550</v>
       </c>
       <c r="D61" s="4">
+        <f t="shared" si="21"/>
+        <v>950</v>
+      </c>
+      <c r="E61" s="4">
+        <f t="shared" si="22"/>
+        <v>78</v>
+      </c>
+      <c r="F61" s="13">
         <f t="shared" si="23"/>
-        <v>950</v>
-      </c>
-      <c r="E61" s="4">
-        <f t="shared" si="24"/>
-        <v>78</v>
-      </c>
-      <c r="F61" s="13">
-        <f t="shared" si="21"/>
-        <v>0.52000000000000035</v>
+        <v>0.64600000000000035</v>
       </c>
       <c r="G61" s="12">
-        <f t="shared" si="22"/>
-        <v>377</v>
+        <f t="shared" si="14"/>
+        <v>533</v>
       </c>
       <c r="I61" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J61" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="K61" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.65500000000000003</v>
       </c>
       <c r="L61" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="M61" s="4">
-        <f t="shared" si="9"/>
-        <v>377</v>
+        <f t="shared" si="8"/>
+        <v>533</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>60</v>
       </c>
       <c r="B62" s="1">
@@ -3501,37 +3501,37 @@
         <v>80</v>
       </c>
       <c r="F62" s="13">
-        <f>F61+0.021</f>
-        <v>0.54100000000000037</v>
+        <f t="shared" si="23"/>
+        <v>0.65200000000000036</v>
       </c>
       <c r="G62" s="12">
-        <f>250+A62*4</f>
-        <v>490</v>
+        <f t="shared" si="14"/>
+        <v>538</v>
       </c>
       <c r="I62" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J62" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
       <c r="K62" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.8</v>
       </c>
       <c r="L62" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M62" s="4">
-        <f t="shared" si="9"/>
-        <v>490</v>
+        <f t="shared" si="8"/>
+        <v>538</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>61</v>
       </c>
       <c r="B63" s="1">
@@ -3550,919 +3550,919 @@
         <v>83</v>
       </c>
       <c r="F63" s="13">
-        <f t="shared" ref="F63:F81" si="26">F62+0.021</f>
-        <v>0.56200000000000039</v>
+        <f>F62+0.006</f>
+        <v>0.65800000000000036</v>
       </c>
       <c r="G63" s="12">
-        <f t="shared" ref="G63:G81" si="27">250+A63*4</f>
-        <v>494</v>
+        <f t="shared" si="14"/>
+        <v>544</v>
       </c>
       <c r="I63" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J63" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
       <c r="K63" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.79</v>
       </c>
       <c r="L63" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.01</v>
       </c>
       <c r="M63" s="4">
-        <f t="shared" si="9"/>
-        <v>494</v>
+        <f t="shared" si="8"/>
+        <v>544</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>62</v>
       </c>
       <c r="B64" s="1">
         <v>2000</v>
       </c>
       <c r="C64" s="1">
-        <f t="shared" ref="C64:C81" si="28">$C$62-D64</f>
+        <f t="shared" ref="C64:C81" si="25">$C$62-D64</f>
         <v>7800</v>
       </c>
       <c r="D64" s="4">
-        <f t="shared" ref="D64:D81" si="29">D63+100</f>
+        <f t="shared" ref="D64:D81" si="26">D63+100</f>
         <v>200</v>
       </c>
       <c r="E64" s="4">
-        <f t="shared" ref="E64:E82" si="30">E63+3</f>
+        <f t="shared" ref="E64:E82" si="27">E63+3</f>
         <v>86</v>
       </c>
       <c r="F64" s="13">
-        <f t="shared" si="26"/>
-        <v>0.58300000000000041</v>
+        <f t="shared" si="23"/>
+        <v>0.66400000000000037</v>
       </c>
       <c r="G64" s="12">
-        <f t="shared" si="27"/>
-        <v>498</v>
+        <f t="shared" si="14"/>
+        <v>549</v>
       </c>
       <c r="I64" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J64" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
       <c r="K64" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.78</v>
       </c>
       <c r="L64" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.02</v>
       </c>
       <c r="M64" s="4">
-        <f t="shared" si="9"/>
-        <v>498</v>
+        <f t="shared" si="8"/>
+        <v>549</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>63</v>
       </c>
       <c r="B65" s="1">
         <v>2000</v>
       </c>
       <c r="C65" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>7700</v>
       </c>
       <c r="D65" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>300</v>
       </c>
       <c r="E65" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>89</v>
       </c>
       <c r="F65" s="13">
-        <f t="shared" si="26"/>
-        <v>0.60400000000000043</v>
+        <f>F64+0.006</f>
+        <v>0.67000000000000037</v>
       </c>
       <c r="G65" s="12">
-        <f t="shared" si="27"/>
-        <v>502</v>
+        <f t="shared" si="14"/>
+        <v>554</v>
       </c>
       <c r="I65" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J65" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
       <c r="K65" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.77</v>
       </c>
       <c r="L65" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.03</v>
       </c>
       <c r="M65" s="4">
-        <f t="shared" si="9"/>
-        <v>502</v>
+        <f t="shared" si="8"/>
+        <v>554</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>64</v>
       </c>
       <c r="B66" s="1">
         <v>2000</v>
       </c>
       <c r="C66" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>7600</v>
       </c>
       <c r="D66" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>400</v>
       </c>
       <c r="E66" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>92</v>
       </c>
       <c r="F66" s="13">
-        <f t="shared" si="26"/>
-        <v>0.62500000000000044</v>
+        <f>F65+0.005</f>
+        <v>0.67500000000000038</v>
       </c>
       <c r="G66" s="12">
-        <f t="shared" si="27"/>
-        <v>506</v>
+        <f t="shared" si="14"/>
+        <v>559</v>
       </c>
       <c r="I66" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J66" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
       <c r="K66" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.76</v>
       </c>
       <c r="L66" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
       <c r="M66" s="4">
-        <f t="shared" si="9"/>
-        <v>506</v>
+        <f t="shared" si="8"/>
+        <v>559</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>65</v>
       </c>
       <c r="B67" s="1">
         <v>2000</v>
       </c>
       <c r="C67" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>7500</v>
       </c>
       <c r="D67" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>500</v>
       </c>
       <c r="E67" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>95</v>
       </c>
       <c r="F67" s="13">
-        <f t="shared" si="26"/>
-        <v>0.64600000000000046</v>
+        <f t="shared" ref="F67:F82" si="28">F66+0.005</f>
+        <v>0.68000000000000038</v>
       </c>
       <c r="G67" s="12">
-        <f t="shared" si="27"/>
-        <v>510</v>
+        <f t="shared" si="14"/>
+        <v>565</v>
       </c>
       <c r="I67" s="4">
-        <f t="shared" ref="I67:I101" si="31">SUM(B67:D67)</f>
+        <f t="shared" ref="I67:I101" si="29">SUM(B67:D67)</f>
         <v>10000</v>
       </c>
       <c r="J67" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
       <c r="K67" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
       <c r="L67" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
       <c r="M67" s="4">
-        <f t="shared" si="9"/>
-        <v>510</v>
+        <f t="shared" si="8"/>
+        <v>565</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>66</v>
       </c>
       <c r="B68" s="1">
         <v>2000</v>
       </c>
       <c r="C68" s="1">
+        <f t="shared" si="25"/>
+        <v>7400</v>
+      </c>
+      <c r="D68" s="4">
+        <f t="shared" si="26"/>
+        <v>600</v>
+      </c>
+      <c r="E68" s="4">
+        <f t="shared" si="27"/>
+        <v>98</v>
+      </c>
+      <c r="F68" s="13">
         <f t="shared" si="28"/>
-        <v>7400</v>
-      </c>
-      <c r="D68" s="4">
+        <v>0.68500000000000039</v>
+      </c>
+      <c r="G68" s="12">
+        <f t="shared" si="14"/>
+        <v>570</v>
+      </c>
+      <c r="I68" s="4">
         <f t="shared" si="29"/>
-        <v>600</v>
-      </c>
-      <c r="E68" s="4">
-        <f t="shared" si="30"/>
-        <v>98</v>
-      </c>
-      <c r="F68" s="13">
-        <f t="shared" si="26"/>
-        <v>0.66700000000000048</v>
-      </c>
-      <c r="G68" s="12">
-        <f t="shared" si="27"/>
-        <v>514</v>
-      </c>
-      <c r="I68" s="4">
-        <f t="shared" si="31"/>
         <v>10000</v>
       </c>
       <c r="J68" s="14">
-        <f t="shared" ref="J68:J100" si="32">B68/10000</f>
+        <f t="shared" ref="J68:J100" si="30">B68/10000</f>
         <v>0.2</v>
       </c>
       <c r="K68" s="14">
-        <f t="shared" ref="K68:K100" si="33">C68/10000</f>
+        <f t="shared" ref="K68:K100" si="31">C68/10000</f>
         <v>0.74</v>
       </c>
       <c r="L68" s="14">
-        <f t="shared" ref="L68:L100" si="34">D68/10000</f>
+        <f t="shared" ref="L68:L100" si="32">D68/10000</f>
         <v>0.06</v>
       </c>
       <c r="M68" s="4">
-        <f t="shared" ref="M68:M100" si="35">G68</f>
-        <v>514</v>
+        <f t="shared" ref="M68:M100" si="33">G68</f>
+        <v>570</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
-        <f t="shared" ref="A69:A74" si="36">A68+1</f>
+        <f t="shared" ref="A69:A74" si="34">A68+1</f>
         <v>67</v>
       </c>
       <c r="B69" s="1">
         <v>2000</v>
       </c>
       <c r="C69" s="1">
+        <f t="shared" si="25"/>
+        <v>7300</v>
+      </c>
+      <c r="D69" s="4">
+        <f t="shared" si="26"/>
+        <v>700</v>
+      </c>
+      <c r="E69" s="4">
+        <f t="shared" si="27"/>
+        <v>101</v>
+      </c>
+      <c r="F69" s="13">
         <f t="shared" si="28"/>
-        <v>7300</v>
-      </c>
-      <c r="D69" s="4">
+        <v>0.69000000000000039</v>
+      </c>
+      <c r="G69" s="12">
+        <f t="shared" ref="G69:G101" si="35">150+ROUNDUP(A69*3.5,0)+ROUNDUP(G68/3,0)</f>
+        <v>575</v>
+      </c>
+      <c r="I69" s="4">
         <f t="shared" si="29"/>
-        <v>700</v>
-      </c>
-      <c r="E69" s="4">
+        <v>10000</v>
+      </c>
+      <c r="J69" s="14">
         <f t="shared" si="30"/>
-        <v>101</v>
-      </c>
-      <c r="F69" s="13">
-        <f t="shared" si="26"/>
-        <v>0.6880000000000005</v>
-      </c>
-      <c r="G69" s="12">
-        <f t="shared" si="27"/>
-        <v>518</v>
-      </c>
-      <c r="I69" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K69" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J69" s="14">
+        <v>0.73</v>
+      </c>
+      <c r="L69" s="14">
         <f t="shared" si="32"/>
-        <v>0.2</v>
-      </c>
-      <c r="K69" s="14">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M69" s="4">
         <f t="shared" si="33"/>
-        <v>0.73</v>
-      </c>
-      <c r="L69" s="14">
-        <f t="shared" si="34"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="M69" s="4">
-        <f t="shared" si="35"/>
-        <v>518</v>
+        <v>575</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>68</v>
       </c>
       <c r="B70" s="1">
         <v>2000</v>
       </c>
       <c r="C70" s="1">
+        <f t="shared" si="25"/>
+        <v>7200</v>
+      </c>
+      <c r="D70" s="4">
+        <f t="shared" si="26"/>
+        <v>800</v>
+      </c>
+      <c r="E70" s="4">
+        <f t="shared" si="27"/>
+        <v>104</v>
+      </c>
+      <c r="F70" s="13">
         <f t="shared" si="28"/>
-        <v>7200</v>
-      </c>
-      <c r="D70" s="4">
+        <v>0.6950000000000004</v>
+      </c>
+      <c r="G70" s="12">
+        <f t="shared" si="35"/>
+        <v>580</v>
+      </c>
+      <c r="I70" s="4">
         <f t="shared" si="29"/>
-        <v>800</v>
-      </c>
-      <c r="E70" s="4">
+        <v>10000</v>
+      </c>
+      <c r="J70" s="14">
         <f t="shared" si="30"/>
-        <v>104</v>
-      </c>
-      <c r="F70" s="13">
-        <f t="shared" si="26"/>
-        <v>0.70900000000000052</v>
-      </c>
-      <c r="G70" s="12">
-        <f t="shared" si="27"/>
-        <v>522</v>
-      </c>
-      <c r="I70" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K70" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J70" s="14">
+        <v>0.72</v>
+      </c>
+      <c r="L70" s="14">
         <f t="shared" si="32"/>
-        <v>0.2</v>
-      </c>
-      <c r="K70" s="14">
+        <v>0.08</v>
+      </c>
+      <c r="M70" s="4">
         <f t="shared" si="33"/>
-        <v>0.72</v>
-      </c>
-      <c r="L70" s="14">
-        <f t="shared" si="34"/>
-        <v>0.08</v>
-      </c>
-      <c r="M70" s="4">
-        <f t="shared" si="35"/>
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>69</v>
       </c>
       <c r="B71" s="1">
         <v>2000</v>
       </c>
       <c r="C71" s="1">
+        <f t="shared" si="25"/>
+        <v>7100</v>
+      </c>
+      <c r="D71" s="4">
+        <f t="shared" si="26"/>
+        <v>900</v>
+      </c>
+      <c r="E71" s="4">
+        <f t="shared" si="27"/>
+        <v>107</v>
+      </c>
+      <c r="F71" s="13">
         <f t="shared" si="28"/>
-        <v>7100</v>
-      </c>
-      <c r="D71" s="4">
+        <v>0.7000000000000004</v>
+      </c>
+      <c r="G71" s="12">
+        <f t="shared" si="35"/>
+        <v>586</v>
+      </c>
+      <c r="I71" s="4">
         <f t="shared" si="29"/>
-        <v>900</v>
-      </c>
-      <c r="E71" s="4">
+        <v>10000</v>
+      </c>
+      <c r="J71" s="14">
         <f t="shared" si="30"/>
-        <v>107</v>
-      </c>
-      <c r="F71" s="13">
-        <f t="shared" si="26"/>
-        <v>0.73000000000000054</v>
-      </c>
-      <c r="G71" s="12">
-        <f t="shared" si="27"/>
-        <v>526</v>
-      </c>
-      <c r="I71" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K71" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J71" s="14">
+        <v>0.71</v>
+      </c>
+      <c r="L71" s="14">
         <f t="shared" si="32"/>
-        <v>0.2</v>
-      </c>
-      <c r="K71" s="14">
+        <v>0.09</v>
+      </c>
+      <c r="M71" s="4">
         <f t="shared" si="33"/>
-        <v>0.71</v>
-      </c>
-      <c r="L71" s="14">
-        <f t="shared" si="34"/>
-        <v>0.09</v>
-      </c>
-      <c r="M71" s="4">
-        <f t="shared" si="35"/>
-        <v>526</v>
+        <v>586</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>70</v>
       </c>
       <c r="B72" s="1">
         <v>2000</v>
       </c>
       <c r="C72" s="1">
+        <f t="shared" si="25"/>
+        <v>7000</v>
+      </c>
+      <c r="D72" s="4">
+        <f t="shared" si="26"/>
+        <v>1000</v>
+      </c>
+      <c r="E72" s="4">
+        <f t="shared" si="27"/>
+        <v>110</v>
+      </c>
+      <c r="F72" s="13">
         <f t="shared" si="28"/>
-        <v>7000</v>
-      </c>
-      <c r="D72" s="4">
+        <v>0.7050000000000004</v>
+      </c>
+      <c r="G72" s="12">
+        <f t="shared" si="35"/>
+        <v>591</v>
+      </c>
+      <c r="I72" s="4">
         <f t="shared" si="29"/>
-        <v>1000</v>
-      </c>
-      <c r="E72" s="4">
+        <v>10000</v>
+      </c>
+      <c r="J72" s="14">
         <f t="shared" si="30"/>
-        <v>110</v>
-      </c>
-      <c r="F72" s="13">
-        <f t="shared" si="26"/>
-        <v>0.75100000000000056</v>
-      </c>
-      <c r="G72" s="12">
-        <f t="shared" si="27"/>
-        <v>530</v>
-      </c>
-      <c r="I72" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K72" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J72" s="14">
+        <v>0.7</v>
+      </c>
+      <c r="L72" s="14">
         <f t="shared" si="32"/>
-        <v>0.2</v>
-      </c>
-      <c r="K72" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="M72" s="4">
         <f t="shared" si="33"/>
-        <v>0.7</v>
-      </c>
-      <c r="L72" s="14">
-        <f t="shared" si="34"/>
-        <v>0.1</v>
-      </c>
-      <c r="M72" s="4">
-        <f t="shared" si="35"/>
-        <v>530</v>
+        <v>591</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>71</v>
       </c>
       <c r="B73" s="1">
         <v>2000</v>
       </c>
       <c r="C73" s="1">
+        <f t="shared" si="25"/>
+        <v>6900</v>
+      </c>
+      <c r="D73" s="4">
+        <f t="shared" si="26"/>
+        <v>1100</v>
+      </c>
+      <c r="E73" s="4">
+        <f t="shared" si="27"/>
+        <v>113</v>
+      </c>
+      <c r="F73" s="13">
         <f t="shared" si="28"/>
-        <v>6900</v>
-      </c>
-      <c r="D73" s="4">
+        <v>0.71000000000000041</v>
+      </c>
+      <c r="G73" s="12">
+        <f t="shared" si="35"/>
+        <v>596</v>
+      </c>
+      <c r="I73" s="4">
         <f t="shared" si="29"/>
-        <v>1100</v>
-      </c>
-      <c r="E73" s="4">
+        <v>10000</v>
+      </c>
+      <c r="J73" s="14">
         <f t="shared" si="30"/>
-        <v>113</v>
-      </c>
-      <c r="F73" s="13">
-        <f t="shared" si="26"/>
-        <v>0.77200000000000057</v>
-      </c>
-      <c r="G73" s="12">
-        <f t="shared" si="27"/>
-        <v>534</v>
-      </c>
-      <c r="I73" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K73" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J73" s="14">
+        <v>0.69</v>
+      </c>
+      <c r="L73" s="14">
         <f t="shared" si="32"/>
-        <v>0.2</v>
-      </c>
-      <c r="K73" s="14">
+        <v>0.11</v>
+      </c>
+      <c r="M73" s="4">
         <f t="shared" si="33"/>
-        <v>0.69</v>
-      </c>
-      <c r="L73" s="14">
-        <f t="shared" si="34"/>
-        <v>0.11</v>
-      </c>
-      <c r="M73" s="4">
-        <f t="shared" si="35"/>
-        <v>534</v>
+        <v>596</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>72</v>
       </c>
       <c r="B74" s="1">
         <v>2000</v>
       </c>
       <c r="C74" s="1">
+        <f t="shared" si="25"/>
+        <v>6800</v>
+      </c>
+      <c r="D74" s="4">
+        <f t="shared" si="26"/>
+        <v>1200</v>
+      </c>
+      <c r="E74" s="4">
+        <f t="shared" si="27"/>
+        <v>116</v>
+      </c>
+      <c r="F74" s="13">
         <f t="shared" si="28"/>
-        <v>6800</v>
-      </c>
-      <c r="D74" s="4">
+        <v>0.71500000000000041</v>
+      </c>
+      <c r="G74" s="12">
+        <f t="shared" si="35"/>
+        <v>601</v>
+      </c>
+      <c r="I74" s="4">
         <f t="shared" si="29"/>
-        <v>1200</v>
-      </c>
-      <c r="E74" s="4">
+        <v>10000</v>
+      </c>
+      <c r="J74" s="14">
         <f t="shared" si="30"/>
-        <v>116</v>
-      </c>
-      <c r="F74" s="13">
-        <f t="shared" si="26"/>
-        <v>0.79300000000000059</v>
-      </c>
-      <c r="G74" s="12">
-        <f t="shared" si="27"/>
-        <v>538</v>
-      </c>
-      <c r="I74" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K74" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J74" s="14">
+        <v>0.68</v>
+      </c>
+      <c r="L74" s="14">
         <f t="shared" si="32"/>
-        <v>0.2</v>
-      </c>
-      <c r="K74" s="14">
+        <v>0.12</v>
+      </c>
+      <c r="M74" s="4">
         <f t="shared" si="33"/>
-        <v>0.68</v>
-      </c>
-      <c r="L74" s="14">
-        <f t="shared" si="34"/>
-        <v>0.12</v>
-      </c>
-      <c r="M74" s="4">
-        <f t="shared" si="35"/>
-        <v>538</v>
+        <v>601</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
-        <f t="shared" ref="A75:A94" si="37">A74+1</f>
+        <f t="shared" ref="A75:A94" si="36">A74+1</f>
         <v>73</v>
       </c>
       <c r="B75" s="1">
         <v>2000</v>
       </c>
       <c r="C75" s="1">
+        <f t="shared" si="25"/>
+        <v>6700</v>
+      </c>
+      <c r="D75" s="4">
+        <f t="shared" si="26"/>
+        <v>1300</v>
+      </c>
+      <c r="E75" s="4">
+        <f t="shared" si="27"/>
+        <v>119</v>
+      </c>
+      <c r="F75" s="13">
         <f t="shared" si="28"/>
-        <v>6700</v>
-      </c>
-      <c r="D75" s="4">
+        <v>0.72000000000000042</v>
+      </c>
+      <c r="G75" s="12">
+        <f t="shared" si="35"/>
+        <v>607</v>
+      </c>
+      <c r="I75" s="4">
         <f t="shared" si="29"/>
-        <v>1300</v>
-      </c>
-      <c r="E75" s="4">
+        <v>10000</v>
+      </c>
+      <c r="J75" s="14">
         <f t="shared" si="30"/>
-        <v>119</v>
-      </c>
-      <c r="F75" s="13">
-        <f t="shared" si="26"/>
-        <v>0.81400000000000061</v>
-      </c>
-      <c r="G75" s="12">
-        <f t="shared" si="27"/>
-        <v>542</v>
-      </c>
-      <c r="I75" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K75" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J75" s="14">
+        <v>0.67</v>
+      </c>
+      <c r="L75" s="14">
         <f t="shared" si="32"/>
-        <v>0.2</v>
-      </c>
-      <c r="K75" s="14">
+        <v>0.13</v>
+      </c>
+      <c r="M75" s="4">
         <f t="shared" si="33"/>
-        <v>0.67</v>
-      </c>
-      <c r="L75" s="14">
-        <f t="shared" si="34"/>
-        <v>0.13</v>
-      </c>
-      <c r="M75" s="4">
-        <f t="shared" si="35"/>
-        <v>542</v>
+        <v>607</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>74</v>
       </c>
       <c r="B76" s="1">
         <v>2000</v>
       </c>
       <c r="C76" s="1">
+        <f t="shared" si="25"/>
+        <v>6600</v>
+      </c>
+      <c r="D76" s="4">
+        <f t="shared" si="26"/>
+        <v>1400</v>
+      </c>
+      <c r="E76" s="4">
+        <f t="shared" si="27"/>
+        <v>122</v>
+      </c>
+      <c r="F76" s="13">
         <f t="shared" si="28"/>
-        <v>6600</v>
-      </c>
-      <c r="D76" s="4">
+        <v>0.72500000000000042</v>
+      </c>
+      <c r="G76" s="12">
+        <f t="shared" si="35"/>
+        <v>612</v>
+      </c>
+      <c r="I76" s="4">
         <f t="shared" si="29"/>
-        <v>1400</v>
-      </c>
-      <c r="E76" s="4">
+        <v>10000</v>
+      </c>
+      <c r="J76" s="14">
         <f t="shared" si="30"/>
-        <v>122</v>
-      </c>
-      <c r="F76" s="13">
-        <f t="shared" si="26"/>
-        <v>0.83500000000000063</v>
-      </c>
-      <c r="G76" s="12">
-        <f t="shared" si="27"/>
-        <v>546</v>
-      </c>
-      <c r="I76" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K76" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J76" s="14">
+        <v>0.66</v>
+      </c>
+      <c r="L76" s="14">
         <f t="shared" si="32"/>
-        <v>0.2</v>
-      </c>
-      <c r="K76" s="14">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M76" s="4">
         <f t="shared" si="33"/>
-        <v>0.66</v>
-      </c>
-      <c r="L76" s="14">
-        <f t="shared" si="34"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="M76" s="4">
-        <f t="shared" si="35"/>
-        <v>546</v>
+        <v>612</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>75</v>
       </c>
       <c r="B77" s="1">
         <v>2000</v>
       </c>
       <c r="C77" s="1">
+        <f t="shared" si="25"/>
+        <v>6500</v>
+      </c>
+      <c r="D77" s="4">
+        <f t="shared" si="26"/>
+        <v>1500</v>
+      </c>
+      <c r="E77" s="4">
+        <f t="shared" si="27"/>
+        <v>125</v>
+      </c>
+      <c r="F77" s="13">
         <f t="shared" si="28"/>
-        <v>6500</v>
-      </c>
-      <c r="D77" s="4">
+        <v>0.73000000000000043</v>
+      </c>
+      <c r="G77" s="12">
+        <f t="shared" si="35"/>
+        <v>617</v>
+      </c>
+      <c r="I77" s="4">
         <f t="shared" si="29"/>
-        <v>1500</v>
-      </c>
-      <c r="E77" s="4">
+        <v>10000</v>
+      </c>
+      <c r="J77" s="14">
         <f t="shared" si="30"/>
-        <v>125</v>
-      </c>
-      <c r="F77" s="13">
-        <f t="shared" si="26"/>
-        <v>0.85600000000000065</v>
-      </c>
-      <c r="G77" s="12">
-        <f t="shared" si="27"/>
-        <v>550</v>
-      </c>
-      <c r="I77" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K77" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J77" s="14">
+        <v>0.65</v>
+      </c>
+      <c r="L77" s="14">
         <f t="shared" si="32"/>
-        <v>0.2</v>
-      </c>
-      <c r="K77" s="14">
+        <v>0.15</v>
+      </c>
+      <c r="M77" s="4">
         <f t="shared" si="33"/>
-        <v>0.65</v>
-      </c>
-      <c r="L77" s="14">
-        <f t="shared" si="34"/>
-        <v>0.15</v>
-      </c>
-      <c r="M77" s="4">
-        <f t="shared" si="35"/>
-        <v>550</v>
+        <v>617</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>76</v>
       </c>
       <c r="B78" s="1">
         <v>2000</v>
       </c>
       <c r="C78" s="1">
+        <f t="shared" si="25"/>
+        <v>6400</v>
+      </c>
+      <c r="D78" s="4">
+        <f t="shared" si="26"/>
+        <v>1600</v>
+      </c>
+      <c r="E78" s="4">
+        <f t="shared" si="27"/>
+        <v>128</v>
+      </c>
+      <c r="F78" s="13">
         <f t="shared" si="28"/>
-        <v>6400</v>
-      </c>
-      <c r="D78" s="4">
+        <v>0.73500000000000043</v>
+      </c>
+      <c r="G78" s="12">
+        <f t="shared" si="35"/>
+        <v>622</v>
+      </c>
+      <c r="I78" s="4">
         <f t="shared" si="29"/>
-        <v>1600</v>
-      </c>
-      <c r="E78" s="4">
+        <v>10000</v>
+      </c>
+      <c r="J78" s="14">
         <f t="shared" si="30"/>
-        <v>128</v>
-      </c>
-      <c r="F78" s="13">
-        <f t="shared" si="26"/>
-        <v>0.87700000000000067</v>
-      </c>
-      <c r="G78" s="12">
-        <f t="shared" si="27"/>
-        <v>554</v>
-      </c>
-      <c r="I78" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K78" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J78" s="14">
+        <v>0.64</v>
+      </c>
+      <c r="L78" s="14">
         <f t="shared" si="32"/>
-        <v>0.2</v>
-      </c>
-      <c r="K78" s="14">
+        <v>0.16</v>
+      </c>
+      <c r="M78" s="4">
         <f t="shared" si="33"/>
-        <v>0.64</v>
-      </c>
-      <c r="L78" s="14">
-        <f t="shared" si="34"/>
-        <v>0.16</v>
-      </c>
-      <c r="M78" s="4">
-        <f t="shared" si="35"/>
-        <v>554</v>
+        <v>622</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>77</v>
       </c>
       <c r="B79" s="1">
         <v>2000</v>
       </c>
       <c r="C79" s="1">
+        <f t="shared" si="25"/>
+        <v>6300</v>
+      </c>
+      <c r="D79" s="4">
+        <f t="shared" si="26"/>
+        <v>1700</v>
+      </c>
+      <c r="E79" s="4">
+        <f t="shared" si="27"/>
+        <v>131</v>
+      </c>
+      <c r="F79" s="13">
         <f t="shared" si="28"/>
-        <v>6300</v>
-      </c>
-      <c r="D79" s="4">
+        <v>0.74000000000000044</v>
+      </c>
+      <c r="G79" s="12">
+        <f t="shared" si="35"/>
+        <v>628</v>
+      </c>
+      <c r="I79" s="4">
         <f t="shared" si="29"/>
-        <v>1700</v>
-      </c>
-      <c r="E79" s="4">
+        <v>10000</v>
+      </c>
+      <c r="J79" s="14">
         <f t="shared" si="30"/>
-        <v>131</v>
-      </c>
-      <c r="F79" s="13">
-        <f t="shared" si="26"/>
-        <v>0.89800000000000069</v>
-      </c>
-      <c r="G79" s="12">
-        <f t="shared" si="27"/>
-        <v>558</v>
-      </c>
-      <c r="I79" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K79" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J79" s="14">
+        <v>0.63</v>
+      </c>
+      <c r="L79" s="14">
         <f t="shared" si="32"/>
-        <v>0.2</v>
-      </c>
-      <c r="K79" s="14">
+        <v>0.17</v>
+      </c>
+      <c r="M79" s="4">
         <f t="shared" si="33"/>
-        <v>0.63</v>
-      </c>
-      <c r="L79" s="14">
-        <f t="shared" si="34"/>
-        <v>0.17</v>
-      </c>
-      <c r="M79" s="4">
-        <f t="shared" si="35"/>
-        <v>558</v>
+        <v>628</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>78</v>
       </c>
       <c r="B80" s="1">
         <v>2000</v>
       </c>
       <c r="C80" s="1">
+        <f t="shared" si="25"/>
+        <v>6200</v>
+      </c>
+      <c r="D80" s="4">
+        <f t="shared" si="26"/>
+        <v>1800</v>
+      </c>
+      <c r="E80" s="4">
+        <f t="shared" si="27"/>
+        <v>134</v>
+      </c>
+      <c r="F80" s="13">
         <f t="shared" si="28"/>
-        <v>6200</v>
-      </c>
-      <c r="D80" s="4">
+        <v>0.74500000000000044</v>
+      </c>
+      <c r="G80" s="12">
+        <f t="shared" si="35"/>
+        <v>633</v>
+      </c>
+      <c r="I80" s="4">
         <f t="shared" si="29"/>
-        <v>1800</v>
-      </c>
-      <c r="E80" s="4">
+        <v>10000</v>
+      </c>
+      <c r="J80" s="14">
         <f t="shared" si="30"/>
-        <v>134</v>
-      </c>
-      <c r="F80" s="13">
-        <f t="shared" si="26"/>
-        <v>0.91900000000000071</v>
-      </c>
-      <c r="G80" s="12">
-        <f t="shared" si="27"/>
-        <v>562</v>
-      </c>
-      <c r="I80" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K80" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J80" s="14">
+        <v>0.62</v>
+      </c>
+      <c r="L80" s="14">
         <f t="shared" si="32"/>
-        <v>0.2</v>
-      </c>
-      <c r="K80" s="14">
+        <v>0.18</v>
+      </c>
+      <c r="M80" s="4">
         <f t="shared" si="33"/>
-        <v>0.62</v>
-      </c>
-      <c r="L80" s="14">
-        <f t="shared" si="34"/>
-        <v>0.18</v>
-      </c>
-      <c r="M80" s="4">
-        <f t="shared" si="35"/>
-        <v>562</v>
+        <v>633</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>79</v>
       </c>
       <c r="B81" s="1">
         <v>2000</v>
       </c>
       <c r="C81" s="1">
+        <f t="shared" si="25"/>
+        <v>6100</v>
+      </c>
+      <c r="D81" s="4">
+        <f t="shared" si="26"/>
+        <v>1900</v>
+      </c>
+      <c r="E81" s="4">
+        <f t="shared" si="27"/>
+        <v>137</v>
+      </c>
+      <c r="F81" s="13">
         <f t="shared" si="28"/>
-        <v>6100</v>
-      </c>
-      <c r="D81" s="4">
+        <v>0.75000000000000044</v>
+      </c>
+      <c r="G81" s="12">
+        <f t="shared" si="35"/>
+        <v>638</v>
+      </c>
+      <c r="I81" s="4">
         <f t="shared" si="29"/>
-        <v>1900</v>
-      </c>
-      <c r="E81" s="4">
+        <v>10000</v>
+      </c>
+      <c r="J81" s="14">
         <f t="shared" si="30"/>
-        <v>137</v>
-      </c>
-      <c r="F81" s="13">
-        <f t="shared" si="26"/>
-        <v>0.94000000000000072</v>
-      </c>
-      <c r="G81" s="12">
-        <f t="shared" si="27"/>
-        <v>566</v>
-      </c>
-      <c r="I81" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K81" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J81" s="14">
+        <v>0.61</v>
+      </c>
+      <c r="L81" s="14">
         <f t="shared" si="32"/>
-        <v>0.2</v>
-      </c>
-      <c r="K81" s="14">
+        <v>0.19</v>
+      </c>
+      <c r="M81" s="4">
         <f t="shared" si="33"/>
-        <v>0.61</v>
-      </c>
-      <c r="L81" s="14">
-        <f t="shared" si="34"/>
-        <v>0.19</v>
-      </c>
-      <c r="M81" s="4">
-        <f t="shared" si="35"/>
-        <v>566</v>
+        <v>638</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>80</v>
       </c>
       <c r="B82" s="1">
@@ -4475,41 +4475,41 @@
         <v>0</v>
       </c>
       <c r="E82" s="4">
+        <f t="shared" si="27"/>
+        <v>140</v>
+      </c>
+      <c r="F82" s="13">
+        <f t="shared" si="28"/>
+        <v>0.75500000000000045</v>
+      </c>
+      <c r="G82" s="12">
+        <f t="shared" si="35"/>
+        <v>643</v>
+      </c>
+      <c r="I82" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J82" s="14">
         <f t="shared" si="30"/>
-        <v>140</v>
-      </c>
-      <c r="F82" s="13">
-        <f>F81+0.036</f>
-        <v>0.97600000000000076</v>
-      </c>
-      <c r="G82" s="12">
-        <f>300+A82*5</f>
-        <v>700</v>
-      </c>
-      <c r="I82" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="K82" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J82" s="14">
+        <v>0.85</v>
+      </c>
+      <c r="L82" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K82" s="14">
+        <v>0</v>
+      </c>
+      <c r="M82" s="4">
         <f t="shared" si="33"/>
-        <v>0.85</v>
-      </c>
-      <c r="L82" s="14">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="M82" s="4">
-        <f t="shared" si="35"/>
-        <v>700</v>
+        <v>643</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>81</v>
       </c>
       <c r="B83" s="1">
@@ -4528,919 +4528,919 @@
         <v>144</v>
       </c>
       <c r="F83" s="13">
-        <f t="shared" ref="F83:F101" si="38">F82+0.036</f>
-        <v>1.0120000000000007</v>
+        <f>F82+0.005</f>
+        <v>0.76000000000000045</v>
       </c>
       <c r="G83" s="12">
-        <f t="shared" ref="G83:G101" si="39">300+A83*5</f>
-        <v>705</v>
+        <f t="shared" si="35"/>
+        <v>649</v>
       </c>
       <c r="I83" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J83" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K83" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J83" s="14">
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="L83" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K83" s="14">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="M83" s="4">
         <f t="shared" si="33"/>
-        <v>0.82899999999999996</v>
-      </c>
-      <c r="L83" s="14">
-        <f t="shared" si="34"/>
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="M83" s="4">
-        <f t="shared" si="35"/>
-        <v>705</v>
+        <v>649</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>82</v>
       </c>
       <c r="B84" s="1">
         <v>1500</v>
       </c>
       <c r="C84" s="1">
-        <f t="shared" ref="C84:C101" si="40">$C$82-D84</f>
+        <f t="shared" ref="C84:C101" si="37">$C$82-D84</f>
         <v>8080</v>
       </c>
       <c r="D84" s="4">
-        <f t="shared" ref="D84:D101" si="41">D83+210</f>
+        <f t="shared" ref="D84:D101" si="38">D83+210</f>
         <v>420</v>
       </c>
       <c r="E84" s="4">
-        <f t="shared" ref="E84:E101" si="42">E83+4</f>
+        <f t="shared" ref="E84:E101" si="39">E83+4</f>
         <v>148</v>
       </c>
       <c r="F84" s="13">
-        <f t="shared" si="38"/>
-        <v>1.0480000000000007</v>
+        <f>F83+0.003</f>
+        <v>0.76300000000000046</v>
       </c>
       <c r="G84" s="12">
-        <f t="shared" si="39"/>
-        <v>710</v>
+        <f t="shared" si="35"/>
+        <v>654</v>
       </c>
       <c r="I84" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J84" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K84" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J84" s="14">
+        <v>0.80800000000000005</v>
+      </c>
+      <c r="L84" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K84" s="14">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="M84" s="4">
         <f t="shared" si="33"/>
-        <v>0.80800000000000005</v>
-      </c>
-      <c r="L84" s="14">
-        <f t="shared" si="34"/>
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="M84" s="4">
-        <f t="shared" si="35"/>
-        <v>710</v>
+        <v>654</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>83</v>
       </c>
       <c r="B85" s="1">
         <v>1500</v>
       </c>
       <c r="C85" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="37"/>
         <v>7870</v>
       </c>
       <c r="D85" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="38"/>
         <v>630</v>
       </c>
       <c r="E85" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="39"/>
         <v>152</v>
       </c>
       <c r="F85" s="13">
-        <f t="shared" si="38"/>
-        <v>1.0840000000000007</v>
+        <f t="shared" ref="F85:F102" si="40">F84+0.003</f>
+        <v>0.76600000000000046</v>
       </c>
       <c r="G85" s="12">
-        <f t="shared" si="39"/>
-        <v>715</v>
+        <f t="shared" si="35"/>
+        <v>659</v>
       </c>
       <c r="I85" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J85" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K85" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J85" s="14">
+        <v>0.78700000000000003</v>
+      </c>
+      <c r="L85" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K85" s="14">
+        <v>6.3E-2</v>
+      </c>
+      <c r="M85" s="4">
         <f t="shared" si="33"/>
-        <v>0.78700000000000003</v>
-      </c>
-      <c r="L85" s="14">
-        <f t="shared" si="34"/>
-        <v>6.3E-2</v>
-      </c>
-      <c r="M85" s="4">
-        <f t="shared" si="35"/>
-        <v>715</v>
+        <v>659</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>84</v>
       </c>
       <c r="B86" s="1">
         <v>1500</v>
       </c>
       <c r="C86" s="1">
+        <f t="shared" si="37"/>
+        <v>7660</v>
+      </c>
+      <c r="D86" s="4">
+        <f t="shared" si="38"/>
+        <v>840</v>
+      </c>
+      <c r="E86" s="4">
+        <f t="shared" si="39"/>
+        <v>156</v>
+      </c>
+      <c r="F86" s="13">
         <f t="shared" si="40"/>
-        <v>7660</v>
-      </c>
-      <c r="D86" s="4">
-        <f t="shared" si="41"/>
-        <v>840</v>
-      </c>
-      <c r="E86" s="4">
-        <f t="shared" si="42"/>
-        <v>156</v>
-      </c>
-      <c r="F86" s="13">
-        <f t="shared" si="38"/>
-        <v>1.1200000000000008</v>
+        <v>0.76900000000000046</v>
       </c>
       <c r="G86" s="12">
-        <f t="shared" si="39"/>
-        <v>720</v>
+        <f t="shared" si="35"/>
+        <v>664</v>
       </c>
       <c r="I86" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J86" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K86" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J86" s="14">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="L86" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K86" s="14">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="M86" s="4">
         <f t="shared" si="33"/>
-        <v>0.76600000000000001</v>
-      </c>
-      <c r="L86" s="14">
-        <f t="shared" si="34"/>
-        <v>8.4000000000000005E-2</v>
-      </c>
-      <c r="M86" s="4">
-        <f t="shared" si="35"/>
-        <v>720</v>
+        <v>664</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>85</v>
       </c>
       <c r="B87" s="1">
         <v>1500</v>
       </c>
       <c r="C87" s="1">
+        <f t="shared" si="37"/>
+        <v>7450</v>
+      </c>
+      <c r="D87" s="4">
+        <f t="shared" si="38"/>
+        <v>1050</v>
+      </c>
+      <c r="E87" s="4">
+        <f t="shared" si="39"/>
+        <v>160</v>
+      </c>
+      <c r="F87" s="13">
         <f t="shared" si="40"/>
-        <v>7450</v>
-      </c>
-      <c r="D87" s="4">
-        <f t="shared" si="41"/>
-        <v>1050</v>
-      </c>
-      <c r="E87" s="4">
-        <f t="shared" si="42"/>
-        <v>160</v>
-      </c>
-      <c r="F87" s="13">
-        <f t="shared" si="38"/>
-        <v>1.1560000000000008</v>
+        <v>0.77200000000000046</v>
       </c>
       <c r="G87" s="12">
-        <f t="shared" si="39"/>
-        <v>725</v>
+        <f t="shared" si="35"/>
+        <v>670</v>
       </c>
       <c r="I87" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J87" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K87" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J87" s="14">
+        <v>0.745</v>
+      </c>
+      <c r="L87" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K87" s="14">
+        <v>0.105</v>
+      </c>
+      <c r="M87" s="4">
         <f t="shared" si="33"/>
-        <v>0.745</v>
-      </c>
-      <c r="L87" s="14">
-        <f t="shared" si="34"/>
-        <v>0.105</v>
-      </c>
-      <c r="M87" s="4">
-        <f t="shared" si="35"/>
-        <v>725</v>
+        <v>670</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>86</v>
       </c>
       <c r="B88" s="1">
         <v>1500</v>
       </c>
       <c r="C88" s="1">
+        <f t="shared" si="37"/>
+        <v>7240</v>
+      </c>
+      <c r="D88" s="4">
+        <f t="shared" si="38"/>
+        <v>1260</v>
+      </c>
+      <c r="E88" s="4">
+        <f t="shared" si="39"/>
+        <v>164</v>
+      </c>
+      <c r="F88" s="13">
         <f t="shared" si="40"/>
-        <v>7240</v>
-      </c>
-      <c r="D88" s="4">
-        <f t="shared" si="41"/>
-        <v>1260</v>
-      </c>
-      <c r="E88" s="4">
-        <f t="shared" si="42"/>
-        <v>164</v>
-      </c>
-      <c r="F88" s="13">
-        <f t="shared" si="38"/>
-        <v>1.1920000000000008</v>
+        <v>0.77500000000000047</v>
       </c>
       <c r="G88" s="12">
-        <f t="shared" si="39"/>
-        <v>730</v>
+        <f t="shared" si="35"/>
+        <v>675</v>
       </c>
       <c r="I88" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J88" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K88" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J88" s="14">
+        <v>0.72399999999999998</v>
+      </c>
+      <c r="L88" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K88" s="14">
+        <v>0.126</v>
+      </c>
+      <c r="M88" s="4">
         <f t="shared" si="33"/>
-        <v>0.72399999999999998</v>
-      </c>
-      <c r="L88" s="14">
-        <f t="shared" si="34"/>
-        <v>0.126</v>
-      </c>
-      <c r="M88" s="4">
-        <f t="shared" si="35"/>
-        <v>730</v>
+        <v>675</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>87</v>
       </c>
       <c r="B89" s="1">
         <v>1500</v>
       </c>
       <c r="C89" s="1">
+        <f t="shared" si="37"/>
+        <v>7030</v>
+      </c>
+      <c r="D89" s="4">
+        <f t="shared" si="38"/>
+        <v>1470</v>
+      </c>
+      <c r="E89" s="4">
+        <f t="shared" si="39"/>
+        <v>168</v>
+      </c>
+      <c r="F89" s="13">
         <f t="shared" si="40"/>
-        <v>7030</v>
-      </c>
-      <c r="D89" s="4">
-        <f t="shared" si="41"/>
-        <v>1470</v>
-      </c>
-      <c r="E89" s="4">
-        <f t="shared" si="42"/>
-        <v>168</v>
-      </c>
-      <c r="F89" s="13">
-        <f t="shared" si="38"/>
-        <v>1.2280000000000009</v>
+        <v>0.77800000000000047</v>
       </c>
       <c r="G89" s="12">
-        <f t="shared" si="39"/>
-        <v>735</v>
+        <f t="shared" si="35"/>
+        <v>680</v>
       </c>
       <c r="I89" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J89" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K89" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J89" s="14">
+        <v>0.70299999999999996</v>
+      </c>
+      <c r="L89" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K89" s="14">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="M89" s="4">
         <f t="shared" si="33"/>
-        <v>0.70299999999999996</v>
-      </c>
-      <c r="L89" s="14">
-        <f t="shared" si="34"/>
-        <v>0.14699999999999999</v>
-      </c>
-      <c r="M89" s="4">
-        <f t="shared" si="35"/>
-        <v>735</v>
+        <v>680</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>88</v>
       </c>
       <c r="B90" s="1">
         <v>1500</v>
       </c>
       <c r="C90" s="1">
+        <f t="shared" si="37"/>
+        <v>6820</v>
+      </c>
+      <c r="D90" s="4">
+        <f t="shared" si="38"/>
+        <v>1680</v>
+      </c>
+      <c r="E90" s="4">
+        <f t="shared" si="39"/>
+        <v>172</v>
+      </c>
+      <c r="F90" s="13">
         <f t="shared" si="40"/>
-        <v>6820</v>
-      </c>
-      <c r="D90" s="4">
-        <f t="shared" si="41"/>
-        <v>1680</v>
-      </c>
-      <c r="E90" s="4">
-        <f t="shared" si="42"/>
-        <v>172</v>
-      </c>
-      <c r="F90" s="13">
-        <f t="shared" si="38"/>
-        <v>1.2640000000000009</v>
+        <v>0.78100000000000047</v>
       </c>
       <c r="G90" s="12">
-        <f t="shared" si="39"/>
-        <v>740</v>
+        <f t="shared" si="35"/>
+        <v>685</v>
       </c>
       <c r="I90" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J90" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K90" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J90" s="14">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="L90" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K90" s="14">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="M90" s="4">
         <f t="shared" si="33"/>
-        <v>0.68200000000000005</v>
-      </c>
-      <c r="L90" s="14">
-        <f t="shared" si="34"/>
-        <v>0.16800000000000001</v>
-      </c>
-      <c r="M90" s="4">
-        <f t="shared" si="35"/>
-        <v>740</v>
+        <v>685</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>89</v>
       </c>
       <c r="B91" s="1">
         <v>1500</v>
       </c>
       <c r="C91" s="1">
+        <f t="shared" si="37"/>
+        <v>6610</v>
+      </c>
+      <c r="D91" s="4">
+        <f t="shared" si="38"/>
+        <v>1890</v>
+      </c>
+      <c r="E91" s="4">
+        <f t="shared" si="39"/>
+        <v>176</v>
+      </c>
+      <c r="F91" s="13">
         <f t="shared" si="40"/>
-        <v>6610</v>
-      </c>
-      <c r="D91" s="4">
-        <f t="shared" si="41"/>
-        <v>1890</v>
-      </c>
-      <c r="E91" s="4">
-        <f t="shared" si="42"/>
-        <v>176</v>
-      </c>
-      <c r="F91" s="13">
-        <f t="shared" si="38"/>
-        <v>1.3000000000000009</v>
+        <v>0.78400000000000047</v>
       </c>
       <c r="G91" s="12">
-        <f t="shared" si="39"/>
-        <v>745</v>
+        <f t="shared" si="35"/>
+        <v>691</v>
       </c>
       <c r="I91" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J91" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K91" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J91" s="14">
+        <v>0.66100000000000003</v>
+      </c>
+      <c r="L91" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K91" s="14">
+        <v>0.189</v>
+      </c>
+      <c r="M91" s="4">
         <f t="shared" si="33"/>
-        <v>0.66100000000000003</v>
-      </c>
-      <c r="L91" s="14">
-        <f t="shared" si="34"/>
-        <v>0.189</v>
-      </c>
-      <c r="M91" s="4">
-        <f t="shared" si="35"/>
-        <v>745</v>
+        <v>691</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>90</v>
       </c>
       <c r="B92" s="1">
         <v>1500</v>
       </c>
       <c r="C92" s="1">
+        <f t="shared" si="37"/>
+        <v>6400</v>
+      </c>
+      <c r="D92" s="4">
+        <f t="shared" si="38"/>
+        <v>2100</v>
+      </c>
+      <c r="E92" s="4">
+        <f t="shared" si="39"/>
+        <v>180</v>
+      </c>
+      <c r="F92" s="13">
         <f t="shared" si="40"/>
-        <v>6400</v>
-      </c>
-      <c r="D92" s="4">
-        <f t="shared" si="41"/>
-        <v>2100</v>
-      </c>
-      <c r="E92" s="4">
-        <f t="shared" si="42"/>
-        <v>180</v>
-      </c>
-      <c r="F92" s="13">
-        <f t="shared" si="38"/>
-        <v>1.336000000000001</v>
+        <v>0.78700000000000048</v>
       </c>
       <c r="G92" s="12">
-        <f t="shared" si="39"/>
-        <v>750</v>
+        <f t="shared" si="35"/>
+        <v>696</v>
       </c>
       <c r="I92" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J92" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K92" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J92" s="14">
+        <v>0.64</v>
+      </c>
+      <c r="L92" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K92" s="14">
+        <v>0.21</v>
+      </c>
+      <c r="M92" s="4">
         <f t="shared" si="33"/>
-        <v>0.64</v>
-      </c>
-      <c r="L92" s="14">
-        <f t="shared" si="34"/>
-        <v>0.21</v>
-      </c>
-      <c r="M92" s="4">
-        <f t="shared" si="35"/>
-        <v>750</v>
+        <v>696</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>91</v>
       </c>
       <c r="B93" s="1">
         <v>1500</v>
       </c>
       <c r="C93" s="1">
+        <f t="shared" si="37"/>
+        <v>6190</v>
+      </c>
+      <c r="D93" s="4">
+        <f t="shared" si="38"/>
+        <v>2310</v>
+      </c>
+      <c r="E93" s="4">
+        <f t="shared" si="39"/>
+        <v>184</v>
+      </c>
+      <c r="F93" s="13">
         <f t="shared" si="40"/>
-        <v>6190</v>
-      </c>
-      <c r="D93" s="4">
-        <f t="shared" si="41"/>
-        <v>2310</v>
-      </c>
-      <c r="E93" s="4">
-        <f t="shared" si="42"/>
-        <v>184</v>
-      </c>
-      <c r="F93" s="13">
-        <f t="shared" si="38"/>
-        <v>1.372000000000001</v>
+        <v>0.79000000000000048</v>
       </c>
       <c r="G93" s="12">
-        <f t="shared" si="39"/>
-        <v>755</v>
+        <f t="shared" si="35"/>
+        <v>701</v>
       </c>
       <c r="I93" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J93" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K93" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J93" s="14">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="L93" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K93" s="14">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="M93" s="4">
         <f t="shared" si="33"/>
-        <v>0.61899999999999999</v>
-      </c>
-      <c r="L93" s="14">
-        <f t="shared" si="34"/>
-        <v>0.23100000000000001</v>
-      </c>
-      <c r="M93" s="4">
-        <f t="shared" si="35"/>
-        <v>755</v>
+        <v>701</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>92</v>
       </c>
       <c r="B94" s="1">
         <v>1500</v>
       </c>
       <c r="C94" s="1">
+        <f t="shared" si="37"/>
+        <v>5980</v>
+      </c>
+      <c r="D94" s="4">
+        <f t="shared" si="38"/>
+        <v>2520</v>
+      </c>
+      <c r="E94" s="4">
+        <f t="shared" si="39"/>
+        <v>188</v>
+      </c>
+      <c r="F94" s="13">
         <f t="shared" si="40"/>
-        <v>5980</v>
-      </c>
-      <c r="D94" s="4">
-        <f t="shared" si="41"/>
-        <v>2520</v>
-      </c>
-      <c r="E94" s="4">
-        <f t="shared" si="42"/>
-        <v>188</v>
-      </c>
-      <c r="F94" s="13">
-        <f t="shared" si="38"/>
-        <v>1.408000000000001</v>
+        <v>0.79300000000000048</v>
       </c>
       <c r="G94" s="12">
-        <f t="shared" si="39"/>
-        <v>760</v>
+        <f t="shared" si="35"/>
+        <v>706</v>
       </c>
       <c r="I94" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J94" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K94" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J94" s="14">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="L94" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K94" s="14">
+        <v>0.252</v>
+      </c>
+      <c r="M94" s="4">
         <f t="shared" si="33"/>
-        <v>0.59799999999999998</v>
-      </c>
-      <c r="L94" s="14">
-        <f t="shared" si="34"/>
-        <v>0.252</v>
-      </c>
-      <c r="M94" s="4">
-        <f t="shared" si="35"/>
-        <v>760</v>
+        <v>706</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
-        <f t="shared" ref="A95:A102" si="43">A94+1</f>
+        <f t="shared" ref="A95:A102" si="41">A94+1</f>
         <v>93</v>
       </c>
       <c r="B95" s="1">
         <v>1500</v>
       </c>
       <c r="C95" s="1">
+        <f t="shared" si="37"/>
+        <v>5770</v>
+      </c>
+      <c r="D95" s="4">
+        <f t="shared" si="38"/>
+        <v>2730</v>
+      </c>
+      <c r="E95" s="4">
+        <f t="shared" si="39"/>
+        <v>192</v>
+      </c>
+      <c r="F95" s="13">
         <f t="shared" si="40"/>
-        <v>5770</v>
-      </c>
-      <c r="D95" s="4">
-        <f t="shared" si="41"/>
-        <v>2730</v>
-      </c>
-      <c r="E95" s="4">
-        <f t="shared" si="42"/>
-        <v>192</v>
-      </c>
-      <c r="F95" s="13">
-        <f t="shared" si="38"/>
-        <v>1.4440000000000011</v>
+        <v>0.79600000000000048</v>
       </c>
       <c r="G95" s="12">
-        <f t="shared" si="39"/>
-        <v>765</v>
+        <f t="shared" si="35"/>
+        <v>712</v>
       </c>
       <c r="I95" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J95" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K95" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J95" s="14">
+        <v>0.57699999999999996</v>
+      </c>
+      <c r="L95" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K95" s="14">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="M95" s="4">
         <f t="shared" si="33"/>
-        <v>0.57699999999999996</v>
-      </c>
-      <c r="L95" s="14">
-        <f t="shared" si="34"/>
-        <v>0.27300000000000002</v>
-      </c>
-      <c r="M95" s="4">
-        <f t="shared" si="35"/>
-        <v>765</v>
+        <v>712</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>94</v>
       </c>
       <c r="B96" s="1">
         <v>1500</v>
       </c>
       <c r="C96" s="1">
+        <f t="shared" si="37"/>
+        <v>5560</v>
+      </c>
+      <c r="D96" s="4">
+        <f t="shared" si="38"/>
+        <v>2940</v>
+      </c>
+      <c r="E96" s="4">
+        <f t="shared" si="39"/>
+        <v>196</v>
+      </c>
+      <c r="F96" s="13">
         <f t="shared" si="40"/>
-        <v>5560</v>
-      </c>
-      <c r="D96" s="4">
-        <f t="shared" si="41"/>
-        <v>2940</v>
-      </c>
-      <c r="E96" s="4">
-        <f t="shared" si="42"/>
-        <v>196</v>
-      </c>
-      <c r="F96" s="13">
-        <f t="shared" si="38"/>
-        <v>1.4800000000000011</v>
+        <v>0.79900000000000049</v>
       </c>
       <c r="G96" s="12">
-        <f t="shared" si="39"/>
-        <v>770</v>
+        <f t="shared" si="35"/>
+        <v>717</v>
       </c>
       <c r="I96" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J96" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K96" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J96" s="14">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="L96" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K96" s="14">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="M96" s="4">
         <f t="shared" si="33"/>
-        <v>0.55600000000000005</v>
-      </c>
-      <c r="L96" s="14">
-        <f t="shared" si="34"/>
-        <v>0.29399999999999998</v>
-      </c>
-      <c r="M96" s="4">
-        <f t="shared" si="35"/>
-        <v>770</v>
+        <v>717</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>95</v>
       </c>
       <c r="B97" s="1">
         <v>1500</v>
       </c>
       <c r="C97" s="1">
+        <f t="shared" si="37"/>
+        <v>5350</v>
+      </c>
+      <c r="D97" s="4">
+        <f t="shared" si="38"/>
+        <v>3150</v>
+      </c>
+      <c r="E97" s="4">
+        <f t="shared" si="39"/>
+        <v>200</v>
+      </c>
+      <c r="F97" s="13">
         <f t="shared" si="40"/>
-        <v>5350</v>
-      </c>
-      <c r="D97" s="4">
-        <f t="shared" si="41"/>
-        <v>3150</v>
-      </c>
-      <c r="E97" s="4">
-        <f t="shared" si="42"/>
-        <v>200</v>
-      </c>
-      <c r="F97" s="13">
-        <f t="shared" si="38"/>
-        <v>1.5160000000000011</v>
+        <v>0.80200000000000049</v>
       </c>
       <c r="G97" s="12">
-        <f t="shared" si="39"/>
-        <v>775</v>
+        <f t="shared" si="35"/>
+        <v>722</v>
       </c>
       <c r="I97" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J97" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K97" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J97" s="14">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="L97" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K97" s="14">
+        <v>0.315</v>
+      </c>
+      <c r="M97" s="4">
         <f t="shared" si="33"/>
-        <v>0.53500000000000003</v>
-      </c>
-      <c r="L97" s="14">
-        <f t="shared" si="34"/>
-        <v>0.315</v>
-      </c>
-      <c r="M97" s="4">
-        <f t="shared" si="35"/>
-        <v>775</v>
+        <v>722</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>96</v>
       </c>
       <c r="B98" s="1">
         <v>1500</v>
       </c>
       <c r="C98" s="1">
+        <f t="shared" si="37"/>
+        <v>5140</v>
+      </c>
+      <c r="D98" s="4">
+        <f t="shared" si="38"/>
+        <v>3360</v>
+      </c>
+      <c r="E98" s="4">
+        <f t="shared" si="39"/>
+        <v>204</v>
+      </c>
+      <c r="F98" s="13">
         <f t="shared" si="40"/>
-        <v>5140</v>
-      </c>
-      <c r="D98" s="4">
-        <f t="shared" si="41"/>
-        <v>3360</v>
-      </c>
-      <c r="E98" s="4">
-        <f t="shared" si="42"/>
-        <v>204</v>
-      </c>
-      <c r="F98" s="13">
-        <f t="shared" si="38"/>
-        <v>1.5520000000000012</v>
+        <v>0.80500000000000049</v>
       </c>
       <c r="G98" s="12">
-        <f t="shared" si="39"/>
-        <v>780</v>
+        <f t="shared" si="35"/>
+        <v>727</v>
       </c>
       <c r="I98" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J98" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K98" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J98" s="14">
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="L98" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K98" s="14">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="M98" s="4">
         <f t="shared" si="33"/>
-        <v>0.51400000000000001</v>
-      </c>
-      <c r="L98" s="14">
-        <f t="shared" si="34"/>
-        <v>0.33600000000000002</v>
-      </c>
-      <c r="M98" s="4">
-        <f t="shared" si="35"/>
-        <v>780</v>
+        <v>727</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>97</v>
       </c>
       <c r="B99" s="1">
         <v>1500</v>
       </c>
       <c r="C99" s="1">
+        <f t="shared" si="37"/>
+        <v>4930</v>
+      </c>
+      <c r="D99" s="4">
+        <f t="shared" si="38"/>
+        <v>3570</v>
+      </c>
+      <c r="E99" s="4">
+        <f t="shared" si="39"/>
+        <v>208</v>
+      </c>
+      <c r="F99" s="13">
         <f t="shared" si="40"/>
-        <v>4930</v>
-      </c>
-      <c r="D99" s="4">
-        <f t="shared" si="41"/>
-        <v>3570</v>
-      </c>
-      <c r="E99" s="4">
-        <f t="shared" si="42"/>
-        <v>208</v>
-      </c>
-      <c r="F99" s="13">
-        <f t="shared" si="38"/>
-        <v>1.5880000000000012</v>
+        <v>0.8080000000000005</v>
       </c>
       <c r="G99" s="12">
-        <f t="shared" si="39"/>
-        <v>785</v>
+        <f t="shared" si="35"/>
+        <v>733</v>
       </c>
       <c r="I99" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J99" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K99" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J99" s="14">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="L99" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K99" s="14">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="M99" s="4">
         <f t="shared" si="33"/>
-        <v>0.49299999999999999</v>
-      </c>
-      <c r="L99" s="14">
-        <f t="shared" si="34"/>
-        <v>0.35699999999999998</v>
-      </c>
-      <c r="M99" s="4">
-        <f t="shared" si="35"/>
-        <v>785</v>
+        <v>733</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>98</v>
       </c>
       <c r="B100" s="1">
         <v>1500</v>
       </c>
       <c r="C100" s="1">
+        <f t="shared" si="37"/>
+        <v>4720</v>
+      </c>
+      <c r="D100" s="4">
+        <f t="shared" si="38"/>
+        <v>3780</v>
+      </c>
+      <c r="E100" s="4">
+        <f t="shared" si="39"/>
+        <v>212</v>
+      </c>
+      <c r="F100" s="13">
         <f t="shared" si="40"/>
-        <v>4720</v>
-      </c>
-      <c r="D100" s="4">
-        <f t="shared" si="41"/>
-        <v>3780</v>
-      </c>
-      <c r="E100" s="4">
-        <f t="shared" si="42"/>
-        <v>212</v>
-      </c>
-      <c r="F100" s="13">
-        <f t="shared" si="38"/>
-        <v>1.6240000000000012</v>
+        <v>0.8110000000000005</v>
       </c>
       <c r="G100" s="12">
-        <f t="shared" si="39"/>
-        <v>790</v>
+        <f t="shared" si="35"/>
+        <v>738</v>
       </c>
       <c r="I100" s="4">
+        <f t="shared" si="29"/>
+        <v>10000</v>
+      </c>
+      <c r="J100" s="14">
+        <f t="shared" si="30"/>
+        <v>0.15</v>
+      </c>
+      <c r="K100" s="14">
         <f t="shared" si="31"/>
-        <v>10000</v>
-      </c>
-      <c r="J100" s="14">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="L100" s="14">
         <f t="shared" si="32"/>
-        <v>0.15</v>
-      </c>
-      <c r="K100" s="14">
+        <v>0.378</v>
+      </c>
+      <c r="M100" s="4">
         <f t="shared" si="33"/>
-        <v>0.47199999999999998</v>
-      </c>
-      <c r="L100" s="14">
-        <f t="shared" si="34"/>
-        <v>0.378</v>
-      </c>
-      <c r="M100" s="4">
-        <f t="shared" si="35"/>
-        <v>790</v>
+        <v>738</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>99</v>
       </c>
       <c r="B101" s="1">
         <v>1500</v>
       </c>
       <c r="C101" s="1">
+        <f t="shared" si="37"/>
+        <v>4510</v>
+      </c>
+      <c r="D101" s="4">
+        <f t="shared" si="38"/>
+        <v>3990</v>
+      </c>
+      <c r="E101" s="4">
+        <f t="shared" si="39"/>
+        <v>216</v>
+      </c>
+      <c r="F101" s="13">
         <f t="shared" si="40"/>
-        <v>4510</v>
-      </c>
-      <c r="D101" s="4">
-        <f t="shared" si="41"/>
-        <v>3990</v>
-      </c>
-      <c r="E101" s="4">
-        <f t="shared" si="42"/>
-        <v>216</v>
-      </c>
-      <c r="F101" s="13">
-        <f t="shared" si="38"/>
-        <v>1.6600000000000013</v>
+        <v>0.8140000000000005</v>
       </c>
       <c r="G101" s="12">
-        <f t="shared" si="39"/>
-        <v>795</v>
+        <f t="shared" si="35"/>
+        <v>743</v>
       </c>
       <c r="I101" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J101" s="14">
-        <f t="shared" ref="J101" si="44">B101/10000</f>
+        <f t="shared" ref="J101" si="42">B101/10000</f>
         <v>0.15</v>
       </c>
       <c r="K101" s="14">
-        <f t="shared" ref="K101" si="45">C101/10000</f>
+        <f t="shared" ref="K101" si="43">C101/10000</f>
         <v>0.45100000000000001</v>
       </c>
       <c r="L101" s="14">
-        <f t="shared" ref="L101" si="46">D101/10000</f>
+        <f t="shared" ref="L101" si="44">D101/10000</f>
         <v>0.39900000000000002</v>
       </c>
       <c r="M101" s="4">
-        <f t="shared" ref="M101" si="47">G101</f>
-        <v>795</v>
+        <f t="shared" ref="M101" si="45">G101</f>
+        <v>743</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="B102" s="5">
@@ -5455,8 +5455,9 @@
       <c r="E102" s="9">
         <v>250</v>
       </c>
-      <c r="F102" s="4">
-        <v>2</v>
+      <c r="F102" s="13">
+        <f t="shared" si="40"/>
+        <v>0.8170000000000005</v>
       </c>
       <c r="G102" s="4">
         <v>-1</v>

--- a/Assets/AddressableResource/Data/Excels/TowerWeaponLevelData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/TowerWeaponLevelData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC9F40C-E176-4E00-9615-18DE7A82BB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0173AF06-1BA7-49AC-AB78-F0E51623EC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -618,8 +618,8 @@
         <v>0.2</v>
       </c>
       <c r="G3" s="12">
-        <f>150+ROUNDUP(A3*3.5,0)</f>
-        <v>154</v>
+        <f>ROUND(300 + (2500-300) * SIN( (A3-1) / 99 * PI() / 2 ), 0)</f>
+        <v>300</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" ref="I3:I34" si="3">SUM(B3:D3)</f>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" s="4">
         <f>G3</f>
-        <v>154</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
@@ -667,425 +667,425 @@
         <v>0.21000000000000002</v>
       </c>
       <c r="G4" s="12">
-        <f>150+ROUNDUP(A4*3.5,0)+ROUNDUP(G3/3,0)</f>
-        <v>209</v>
+        <f t="shared" ref="G4:G67" si="5">ROUND(300 + (2500-300) * SIN( (A4-1) / 99 * PI() / 2 ), 0)</f>
+        <v>335</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J4" s="14">
-        <f t="shared" ref="J4:J67" si="5">B4/10000</f>
+        <f t="shared" ref="J4:J67" si="6">B4/10000</f>
         <v>0.9</v>
       </c>
       <c r="K4" s="14">
-        <f t="shared" ref="K4:K67" si="6">C4/10000</f>
+        <f t="shared" ref="K4:K67" si="7">C4/10000</f>
         <v>0.1</v>
       </c>
       <c r="L4" s="14">
-        <f t="shared" ref="L4:L67" si="7">D4/10000</f>
+        <f t="shared" ref="L4:L67" si="8">D4/10000</f>
         <v>0</v>
       </c>
       <c r="M4" s="4">
-        <f t="shared" ref="M4:M67" si="8">G4</f>
-        <v>209</v>
+        <f t="shared" ref="M4:M67" si="9">G4</f>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <f t="shared" ref="A5:A68" si="9">A4+1</f>
+        <f t="shared" ref="A5:A68" si="10">A4+1</f>
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <f t="shared" ref="B5:B12" si="10">B4-500</f>
+        <f t="shared" ref="B5:B12" si="11">B4-500</f>
         <v>8500</v>
       </c>
       <c r="C5" s="1">
-        <f t="shared" ref="C5:C12" si="11">C4+500</f>
+        <f t="shared" ref="C5:C12" si="12">C4+500</f>
         <v>1500</v>
       </c>
       <c r="D5" s="4">
         <v>0</v>
       </c>
       <c r="E5" s="4">
-        <f t="shared" ref="E5:E42" si="12">E4+1</f>
+        <f t="shared" ref="E5:E42" si="13">E4+1</f>
         <v>3</v>
       </c>
       <c r="F5" s="13">
-        <f t="shared" ref="F5:F22" si="13">F4+0.01</f>
+        <f t="shared" ref="F5:F13" si="14">F4+0.01</f>
         <v>0.22000000000000003</v>
       </c>
       <c r="G5" s="12">
-        <f t="shared" ref="G5:G68" si="14">150+ROUNDUP(A5*3.5,0)+ROUNDUP(G4/3,0)</f>
-        <v>231</v>
+        <f t="shared" si="5"/>
+        <v>370</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J5" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.85</v>
       </c>
       <c r="K5" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
       <c r="L5" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M5" s="4">
-        <f t="shared" si="8"/>
-        <v>231</v>
+        <f t="shared" si="9"/>
+        <v>370</v>
       </c>
     </row>
     <row r="6" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="B6" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8000</v>
       </c>
       <c r="C6" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2000</v>
       </c>
       <c r="D6" s="4">
         <v>0</v>
       </c>
       <c r="E6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="F6" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.23000000000000004</v>
       </c>
       <c r="G6" s="12">
-        <f t="shared" si="14"/>
-        <v>241</v>
+        <f t="shared" si="5"/>
+        <v>405</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J6" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.8</v>
       </c>
       <c r="K6" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
       <c r="L6" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M6" s="4">
-        <f t="shared" si="8"/>
-        <v>241</v>
+        <f t="shared" si="9"/>
+        <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="B7" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7500</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2500</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
       </c>
       <c r="E7" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
       <c r="F7" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.24000000000000005</v>
       </c>
       <c r="G7" s="12">
-        <f t="shared" si="14"/>
-        <v>249</v>
+        <f t="shared" si="5"/>
+        <v>440</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J7" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
       <c r="K7" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.25</v>
       </c>
       <c r="L7" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M7" s="4">
-        <f t="shared" si="8"/>
-        <v>249</v>
+        <f t="shared" si="9"/>
+        <v>440</v>
       </c>
     </row>
     <row r="8" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="B8" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7000</v>
       </c>
       <c r="C8" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3000</v>
       </c>
       <c r="D8" s="4">
         <v>0</v>
       </c>
       <c r="E8" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6</v>
       </c>
       <c r="F8" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="G8" s="12">
-        <f t="shared" si="14"/>
-        <v>254</v>
+        <f t="shared" si="5"/>
+        <v>474</v>
       </c>
       <c r="I8" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J8" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.7</v>
       </c>
       <c r="K8" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.3</v>
       </c>
       <c r="L8" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M8" s="4">
-        <f t="shared" si="8"/>
-        <v>254</v>
+        <f t="shared" si="9"/>
+        <v>474</v>
       </c>
     </row>
     <row r="9" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
       <c r="B9" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6500</v>
       </c>
       <c r="C9" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3500</v>
       </c>
       <c r="D9" s="4">
         <v>0</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
       <c r="F9" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.26000000000000006</v>
       </c>
       <c r="G9" s="12">
-        <f t="shared" si="14"/>
-        <v>260</v>
+        <f t="shared" si="5"/>
+        <v>509</v>
       </c>
       <c r="I9" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J9" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.65</v>
       </c>
       <c r="K9" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.35</v>
       </c>
       <c r="L9" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M9" s="4">
-        <f t="shared" si="8"/>
-        <v>260</v>
+        <f t="shared" si="9"/>
+        <v>509</v>
       </c>
     </row>
     <row r="10" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="B10" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6000</v>
       </c>
       <c r="C10" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="D10" s="4">
         <v>0</v>
       </c>
       <c r="E10" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
       <c r="F10" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.27000000000000007</v>
       </c>
       <c r="G10" s="12">
-        <f t="shared" si="14"/>
-        <v>265</v>
+        <f t="shared" si="5"/>
+        <v>544</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J10" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
       <c r="K10" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="L10" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M10" s="4">
-        <f t="shared" si="8"/>
-        <v>265</v>
+        <f t="shared" si="9"/>
+        <v>544</v>
       </c>
     </row>
     <row r="11" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="B11" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5500</v>
       </c>
       <c r="C11" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4500</v>
       </c>
       <c r="D11" s="4">
         <v>0</v>
       </c>
       <c r="E11" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="F11" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.28000000000000008</v>
       </c>
       <c r="G11" s="12">
-        <f t="shared" si="14"/>
-        <v>271</v>
+        <f t="shared" si="5"/>
+        <v>579</v>
       </c>
       <c r="I11" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J11" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="K11" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.45</v>
       </c>
       <c r="L11" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M11" s="4">
-        <f t="shared" si="8"/>
-        <v>271</v>
+        <f t="shared" si="9"/>
+        <v>579</v>
       </c>
     </row>
     <row r="12" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="B12" s="1">
-        <f t="shared" si="10"/>
-        <v>5000</v>
-      </c>
-      <c r="C12" s="1">
         <f t="shared" si="11"/>
         <v>5000</v>
       </c>
+      <c r="C12" s="1">
+        <f t="shared" si="12"/>
+        <v>5000</v>
+      </c>
       <c r="D12" s="4">
         <v>0</v>
       </c>
       <c r="E12" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="F12" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.29000000000000009</v>
       </c>
       <c r="G12" s="12">
-        <f t="shared" si="14"/>
-        <v>276</v>
+        <f t="shared" si="5"/>
+        <v>613</v>
       </c>
       <c r="I12" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J12" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="K12" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="L12" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M12" s="4">
-        <f t="shared" si="8"/>
-        <v>276</v>
+        <f t="shared" si="9"/>
+        <v>613</v>
       </c>
     </row>
     <row r="13" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="B13" s="1">
@@ -1100,41 +1100,41 @@
         <v>0</v>
       </c>
       <c r="E13" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11</v>
       </c>
       <c r="F13" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.3000000000000001</v>
       </c>
       <c r="G13" s="12">
-        <f t="shared" si="14"/>
-        <v>281</v>
+        <f t="shared" si="5"/>
+        <v>648</v>
       </c>
       <c r="I13" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J13" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.48</v>
       </c>
       <c r="K13" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.52</v>
       </c>
       <c r="L13" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M13" s="4">
-        <f t="shared" si="8"/>
-        <v>281</v>
+        <f t="shared" si="9"/>
+        <v>648</v>
       </c>
     </row>
     <row r="14" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="B14" s="1">
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
       <c r="F14" s="13">
@@ -1157,33 +1157,33 @@
         <v>0.30800000000000011</v>
       </c>
       <c r="G14" s="12">
-        <f t="shared" si="14"/>
-        <v>286</v>
+        <f t="shared" si="5"/>
+        <v>682</v>
       </c>
       <c r="I14" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.46</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.54</v>
       </c>
       <c r="L14" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M14" s="4">
-        <f t="shared" si="8"/>
-        <v>286</v>
+        <f t="shared" si="9"/>
+        <v>682</v>
       </c>
     </row>
     <row r="15" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
       <c r="B15" s="1">
@@ -1198,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
       <c r="F15" s="13">
@@ -1206,33 +1206,33 @@
         <v>0.31600000000000011</v>
       </c>
       <c r="G15" s="12">
-        <f t="shared" si="14"/>
-        <v>292</v>
+        <f t="shared" si="5"/>
+        <v>716</v>
       </c>
       <c r="I15" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J15" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.44</v>
       </c>
       <c r="K15" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="L15" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M15" s="4">
-        <f t="shared" si="8"/>
-        <v>292</v>
+        <f t="shared" si="9"/>
+        <v>716</v>
       </c>
     </row>
     <row r="16" spans="1:13 16382:16382" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="B16" s="1">
@@ -1247,7 +1247,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
       <c r="F16" s="13">
@@ -1255,33 +1255,33 @@
         <v>0.32400000000000012</v>
       </c>
       <c r="G16" s="12">
-        <f t="shared" si="14"/>
-        <v>297</v>
+        <f t="shared" si="5"/>
+        <v>751</v>
       </c>
       <c r="I16" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J16" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.42</v>
       </c>
       <c r="K16" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="L16" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M16" s="4">
-        <f t="shared" si="8"/>
-        <v>297</v>
+        <f t="shared" si="9"/>
+        <v>751</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="B17" s="1">
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15</v>
       </c>
       <c r="F17" s="13">
@@ -1304,33 +1304,33 @@
         <v>0.33200000000000013</v>
       </c>
       <c r="G17" s="12">
-        <f t="shared" si="14"/>
-        <v>302</v>
+        <f t="shared" si="5"/>
+        <v>785</v>
       </c>
       <c r="I17" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J17" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.4</v>
       </c>
       <c r="K17" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="L17" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M17" s="4">
-        <f t="shared" si="8"/>
-        <v>302</v>
+        <f t="shared" si="9"/>
+        <v>785</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>16</v>
       </c>
       <c r="B18" s="1">
@@ -1345,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>16</v>
       </c>
       <c r="F18" s="13">
@@ -1353,33 +1353,33 @@
         <v>0.34000000000000014</v>
       </c>
       <c r="G18" s="12">
-        <f t="shared" si="14"/>
-        <v>307</v>
+        <f t="shared" si="5"/>
+        <v>819</v>
       </c>
       <c r="I18" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J18" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.38</v>
       </c>
       <c r="K18" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.62</v>
       </c>
       <c r="L18" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M18" s="4">
-        <f t="shared" si="8"/>
-        <v>307</v>
+        <f t="shared" si="9"/>
+        <v>819</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>17</v>
       </c>
       <c r="B19" s="1">
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>17</v>
       </c>
       <c r="F19" s="13">
@@ -1402,33 +1402,33 @@
         <v>0.34800000000000014</v>
       </c>
       <c r="G19" s="12">
-        <f t="shared" si="14"/>
-        <v>313</v>
+        <f t="shared" si="5"/>
+        <v>853</v>
       </c>
       <c r="I19" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J19" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.36</v>
       </c>
       <c r="K19" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.64</v>
       </c>
       <c r="L19" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M19" s="4">
-        <f t="shared" si="8"/>
-        <v>313</v>
+        <f t="shared" si="9"/>
+        <v>853</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="B20" s="1">
@@ -1443,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>18</v>
       </c>
       <c r="F20" s="13">
@@ -1451,33 +1451,33 @@
         <v>0.35600000000000015</v>
       </c>
       <c r="G20" s="12">
-        <f t="shared" si="14"/>
-        <v>318</v>
+        <f t="shared" si="5"/>
+        <v>886</v>
       </c>
       <c r="I20" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J20" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.34</v>
       </c>
       <c r="K20" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.66</v>
       </c>
       <c r="L20" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M20" s="4">
-        <f t="shared" si="8"/>
-        <v>318</v>
+        <f t="shared" si="9"/>
+        <v>886</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="B21" s="1">
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>19</v>
       </c>
       <c r="F21" s="13">
@@ -1500,33 +1500,33 @@
         <v>0.36400000000000016</v>
       </c>
       <c r="G21" s="12">
-        <f t="shared" si="14"/>
-        <v>323</v>
+        <f t="shared" si="5"/>
+        <v>920</v>
       </c>
       <c r="I21" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J21" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.32</v>
       </c>
       <c r="K21" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
       <c r="L21" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M21" s="4">
-        <f t="shared" si="8"/>
-        <v>323</v>
+        <f t="shared" si="9"/>
+        <v>920</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="B22" s="1">
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
       <c r="F22" s="13">
@@ -1549,33 +1549,33 @@
         <v>0.37200000000000016</v>
       </c>
       <c r="G22" s="12">
-        <f t="shared" si="14"/>
-        <v>328</v>
+        <f t="shared" si="5"/>
+        <v>953</v>
       </c>
       <c r="I22" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J22" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K22" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.7</v>
       </c>
       <c r="L22" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M22" s="4">
-        <f t="shared" si="8"/>
-        <v>328</v>
+        <f t="shared" si="9"/>
+        <v>953</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="B23" s="1">
@@ -1590,7 +1590,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>21</v>
       </c>
       <c r="F23" s="13">
@@ -1598,33 +1598,33 @@
         <v>0.38000000000000017</v>
       </c>
       <c r="G23" s="12">
-        <f t="shared" si="14"/>
-        <v>334</v>
+        <f t="shared" si="5"/>
+        <v>986</v>
       </c>
       <c r="I23" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J23" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K23" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.69799999999999995</v>
       </c>
       <c r="L23" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2E-3</v>
       </c>
       <c r="M23" s="4">
-        <f t="shared" si="8"/>
-        <v>334</v>
+        <f t="shared" si="9"/>
+        <v>986</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>22</v>
       </c>
       <c r="B24" s="1">
@@ -1639,7 +1639,7 @@
         <v>40</v>
       </c>
       <c r="E24" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>22</v>
       </c>
       <c r="F24" s="13">
@@ -1647,33 +1647,33 @@
         <v>0.38800000000000018</v>
       </c>
       <c r="G24" s="12">
-        <f t="shared" si="14"/>
-        <v>339</v>
+        <f t="shared" si="5"/>
+        <v>1020</v>
       </c>
       <c r="I24" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J24" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K24" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.69599999999999995</v>
       </c>
       <c r="L24" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="M24" s="4">
-        <f t="shared" si="8"/>
-        <v>339</v>
+        <f t="shared" si="9"/>
+        <v>1020</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>23</v>
       </c>
       <c r="B25" s="1">
@@ -1688,7 +1688,7 @@
         <v>60</v>
       </c>
       <c r="E25" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>23</v>
       </c>
       <c r="F25" s="13">
@@ -1696,33 +1696,33 @@
         <v>0.39600000000000019</v>
       </c>
       <c r="G25" s="12">
-        <f t="shared" si="14"/>
-        <v>344</v>
+        <f t="shared" si="5"/>
+        <v>1052</v>
       </c>
       <c r="I25" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J25" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K25" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.69399999999999995</v>
       </c>
       <c r="L25" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="M25" s="4">
-        <f t="shared" si="8"/>
-        <v>344</v>
+        <f t="shared" si="9"/>
+        <v>1052</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>24</v>
       </c>
       <c r="B26" s="1">
@@ -1737,7 +1737,7 @@
         <v>80</v>
       </c>
       <c r="E26" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>24</v>
       </c>
       <c r="F26" s="13">
@@ -1745,33 +1745,33 @@
         <v>0.40400000000000019</v>
       </c>
       <c r="G26" s="12">
-        <f t="shared" si="14"/>
-        <v>349</v>
+        <f t="shared" si="5"/>
+        <v>1085</v>
       </c>
       <c r="I26" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J26" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K26" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.69199999999999995</v>
       </c>
       <c r="L26" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="M26" s="4">
-        <f t="shared" si="8"/>
-        <v>349</v>
+        <f t="shared" si="9"/>
+        <v>1085</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>25</v>
       </c>
       <c r="B27" s="1">
@@ -1786,7 +1786,7 @@
         <v>100</v>
       </c>
       <c r="E27" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>25</v>
       </c>
       <c r="F27" s="13">
@@ -1794,33 +1794,33 @@
         <v>0.4120000000000002</v>
       </c>
       <c r="G27" s="12">
-        <f t="shared" si="14"/>
-        <v>355</v>
+        <f t="shared" si="5"/>
+        <v>1118</v>
       </c>
       <c r="I27" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J27" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K27" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.69</v>
       </c>
       <c r="L27" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.01</v>
       </c>
       <c r="M27" s="4">
-        <f t="shared" si="8"/>
-        <v>355</v>
+        <f t="shared" si="9"/>
+        <v>1118</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>26</v>
       </c>
       <c r="B28" s="1">
@@ -1835,7 +1835,7 @@
         <v>120</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>26</v>
       </c>
       <c r="F28" s="13">
@@ -1843,33 +1843,33 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="G28" s="12">
-        <f t="shared" si="14"/>
-        <v>360</v>
+        <f t="shared" si="5"/>
+        <v>1150</v>
       </c>
       <c r="I28" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J28" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K28" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.68799999999999994</v>
       </c>
       <c r="L28" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2E-2</v>
       </c>
       <c r="M28" s="4">
-        <f t="shared" si="8"/>
-        <v>360</v>
+        <f t="shared" si="9"/>
+        <v>1150</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>27</v>
       </c>
       <c r="B29" s="1">
@@ -1884,7 +1884,7 @@
         <v>140</v>
       </c>
       <c r="E29" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>27</v>
       </c>
       <c r="F29" s="13">
@@ -1892,33 +1892,33 @@
         <v>0.42800000000000021</v>
       </c>
       <c r="G29" s="12">
-        <f t="shared" si="14"/>
-        <v>365</v>
+        <f t="shared" si="5"/>
+        <v>1182</v>
       </c>
       <c r="I29" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J29" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K29" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.68600000000000005</v>
       </c>
       <c r="L29" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4E-2</v>
       </c>
       <c r="M29" s="4">
-        <f t="shared" si="8"/>
-        <v>365</v>
+        <f t="shared" si="9"/>
+        <v>1182</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>28</v>
       </c>
       <c r="B30" s="1">
@@ -1933,7 +1933,7 @@
         <v>160</v>
       </c>
       <c r="E30" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>28</v>
       </c>
       <c r="F30" s="13">
@@ -1941,33 +1941,33 @@
         <v>0.43600000000000022</v>
       </c>
       <c r="G30" s="12">
-        <f t="shared" si="14"/>
-        <v>370</v>
+        <f t="shared" si="5"/>
+        <v>1214</v>
       </c>
       <c r="I30" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J30" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K30" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.68400000000000005</v>
       </c>
       <c r="L30" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.6E-2</v>
       </c>
       <c r="M30" s="4">
-        <f t="shared" si="8"/>
-        <v>370</v>
+        <f t="shared" si="9"/>
+        <v>1214</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>29</v>
       </c>
       <c r="B31" s="1">
@@ -1982,7 +1982,7 @@
         <v>180</v>
       </c>
       <c r="E31" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>29</v>
       </c>
       <c r="F31" s="13">
@@ -1990,33 +1990,33 @@
         <v>0.44400000000000023</v>
       </c>
       <c r="G31" s="12">
-        <f t="shared" si="14"/>
-        <v>376</v>
+        <f t="shared" si="5"/>
+        <v>1246</v>
       </c>
       <c r="I31" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J31" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K31" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.68200000000000005</v>
       </c>
       <c r="L31" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="M31" s="4">
-        <f t="shared" si="8"/>
-        <v>376</v>
+        <f t="shared" si="9"/>
+        <v>1246</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="B32" s="1">
@@ -2031,7 +2031,7 @@
         <v>200</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>30</v>
       </c>
       <c r="F32" s="13">
@@ -2039,33 +2039,33 @@
         <v>0.45200000000000023</v>
       </c>
       <c r="G32" s="12">
-        <f t="shared" si="14"/>
-        <v>381</v>
+        <f t="shared" si="5"/>
+        <v>1277</v>
       </c>
       <c r="I32" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J32" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K32" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
       <c r="L32" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.02</v>
       </c>
       <c r="M32" s="4">
-        <f t="shared" si="8"/>
-        <v>381</v>
+        <f t="shared" si="9"/>
+        <v>1277</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="B33" s="1">
@@ -2080,7 +2080,7 @@
         <v>220</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="F33" s="13">
@@ -2088,33 +2088,33 @@
         <v>0.46000000000000024</v>
       </c>
       <c r="G33" s="12">
-        <f t="shared" si="14"/>
-        <v>386</v>
+        <f t="shared" si="5"/>
+        <v>1308</v>
       </c>
       <c r="I33" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J33" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K33" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.67800000000000005</v>
       </c>
       <c r="L33" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="M33" s="4">
-        <f t="shared" si="8"/>
-        <v>386</v>
+        <f t="shared" si="9"/>
+        <v>1308</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>32</v>
       </c>
       <c r="B34" s="1">
@@ -2129,7 +2129,7 @@
         <v>240</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>32</v>
       </c>
       <c r="F34" s="13">
@@ -2137,33 +2137,33 @@
         <v>0.46800000000000025</v>
       </c>
       <c r="G34" s="12">
-        <f t="shared" si="14"/>
-        <v>391</v>
+        <f t="shared" si="5"/>
+        <v>1339</v>
       </c>
       <c r="I34" s="4">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
       <c r="J34" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K34" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.67600000000000005</v>
       </c>
       <c r="L34" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.4E-2</v>
       </c>
       <c r="M34" s="4">
-        <f t="shared" si="8"/>
-        <v>391</v>
+        <f t="shared" si="9"/>
+        <v>1339</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>33</v>
       </c>
       <c r="B35" s="1">
@@ -2178,7 +2178,7 @@
         <v>260</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>33</v>
       </c>
       <c r="F35" s="13">
@@ -2186,33 +2186,33 @@
         <v>0.47600000000000026</v>
       </c>
       <c r="G35" s="12">
-        <f t="shared" si="14"/>
-        <v>397</v>
+        <f t="shared" si="5"/>
+        <v>1370</v>
       </c>
       <c r="I35" s="4">
         <f t="shared" ref="I35:I66" si="20">SUM(B35:D35)</f>
         <v>10000</v>
       </c>
       <c r="J35" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K35" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.67400000000000004</v>
       </c>
       <c r="L35" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="M35" s="4">
-        <f t="shared" si="8"/>
-        <v>397</v>
+        <f t="shared" si="9"/>
+        <v>1370</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>34</v>
       </c>
       <c r="B36" s="1">
@@ -2227,7 +2227,7 @@
         <v>280</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>34</v>
       </c>
       <c r="F36" s="13">
@@ -2235,33 +2235,33 @@
         <v>0.48400000000000026</v>
       </c>
       <c r="G36" s="12">
-        <f t="shared" si="14"/>
-        <v>402</v>
+        <f t="shared" si="5"/>
+        <v>1400</v>
       </c>
       <c r="I36" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J36" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K36" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.67200000000000004</v>
       </c>
       <c r="L36" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="M36" s="4">
-        <f t="shared" si="8"/>
-        <v>402</v>
+        <f t="shared" si="9"/>
+        <v>1400</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>35</v>
       </c>
       <c r="B37" s="1">
@@ -2276,7 +2276,7 @@
         <v>300</v>
       </c>
       <c r="E37" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>35</v>
       </c>
       <c r="F37" s="13">
@@ -2284,33 +2284,33 @@
         <v>0.49200000000000027</v>
       </c>
       <c r="G37" s="12">
-        <f t="shared" si="14"/>
-        <v>407</v>
+        <f t="shared" si="5"/>
+        <v>1430</v>
       </c>
       <c r="I37" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J37" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K37" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.67</v>
       </c>
       <c r="L37" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.03</v>
       </c>
       <c r="M37" s="4">
-        <f t="shared" si="8"/>
-        <v>407</v>
+        <f t="shared" si="9"/>
+        <v>1430</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>36</v>
       </c>
       <c r="B38" s="1">
@@ -2325,7 +2325,7 @@
         <v>320</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>36</v>
       </c>
       <c r="F38" s="13">
@@ -2333,33 +2333,33 @@
         <v>0.50000000000000022</v>
       </c>
       <c r="G38" s="12">
-        <f t="shared" si="14"/>
-        <v>412</v>
+        <f t="shared" si="5"/>
+        <v>1460</v>
       </c>
       <c r="I38" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J38" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K38" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.66800000000000004</v>
       </c>
       <c r="L38" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="M38" s="4">
-        <f t="shared" si="8"/>
-        <v>412</v>
+        <f t="shared" si="9"/>
+        <v>1460</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
       <c r="B39" s="1">
@@ -2374,7 +2374,7 @@
         <v>340</v>
       </c>
       <c r="E39" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>37</v>
       </c>
       <c r="F39" s="13">
@@ -2382,33 +2382,33 @@
         <v>0.50800000000000023</v>
       </c>
       <c r="G39" s="12">
-        <f t="shared" si="14"/>
-        <v>418</v>
+        <f t="shared" si="5"/>
+        <v>1489</v>
       </c>
       <c r="I39" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J39" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K39" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.66600000000000004</v>
       </c>
       <c r="L39" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="M39" s="4">
-        <f t="shared" si="8"/>
-        <v>418</v>
+        <f t="shared" si="9"/>
+        <v>1489</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>38</v>
       </c>
       <c r="B40" s="1">
@@ -2423,7 +2423,7 @@
         <v>360</v>
       </c>
       <c r="E40" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>38</v>
       </c>
       <c r="F40" s="13">
@@ -2431,33 +2431,33 @@
         <v>0.51600000000000024</v>
       </c>
       <c r="G40" s="12">
-        <f t="shared" si="14"/>
-        <v>423</v>
+        <f t="shared" si="5"/>
+        <v>1519</v>
       </c>
       <c r="I40" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J40" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K40" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.66400000000000003</v>
       </c>
       <c r="L40" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="M40" s="4">
-        <f t="shared" si="8"/>
-        <v>423</v>
+        <f t="shared" si="9"/>
+        <v>1519</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>39</v>
       </c>
       <c r="B41" s="1">
@@ -2472,7 +2472,7 @@
         <v>380</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>39</v>
       </c>
       <c r="F41" s="13">
@@ -2480,33 +2480,33 @@
         <v>0.52400000000000024</v>
       </c>
       <c r="G41" s="12">
-        <f t="shared" si="14"/>
-        <v>428</v>
+        <f t="shared" si="5"/>
+        <v>1548</v>
       </c>
       <c r="I41" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J41" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K41" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.66200000000000003</v>
       </c>
       <c r="L41" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="M41" s="4">
-        <f t="shared" si="8"/>
-        <v>428</v>
+        <f t="shared" si="9"/>
+        <v>1548</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
       <c r="B42" s="1">
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>40</v>
       </c>
       <c r="F42" s="13">
@@ -2527,33 +2527,33 @@
         <v>0.53200000000000025</v>
       </c>
       <c r="G42" s="12">
-        <f t="shared" si="14"/>
-        <v>433</v>
+        <f t="shared" si="5"/>
+        <v>1576</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J42" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K42" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
       <c r="L42" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M42" s="4">
-        <f t="shared" si="8"/>
-        <v>433</v>
+        <f t="shared" si="9"/>
+        <v>1576</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>41</v>
       </c>
       <c r="B43" s="1">
@@ -2576,33 +2576,33 @@
         <v>0.53800000000000026</v>
       </c>
       <c r="G43" s="12">
-        <f t="shared" si="14"/>
-        <v>439</v>
+        <f t="shared" si="5"/>
+        <v>1604</v>
       </c>
       <c r="I43" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J43" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K43" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.745</v>
       </c>
       <c r="L43" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="M43" s="4">
-        <f t="shared" si="8"/>
-        <v>439</v>
+        <f t="shared" si="9"/>
+        <v>1604</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>42</v>
       </c>
       <c r="B44" s="1">
@@ -2625,33 +2625,33 @@
         <v>0.54400000000000026</v>
       </c>
       <c r="G44" s="12">
-        <f t="shared" si="14"/>
-        <v>444</v>
+        <f t="shared" si="5"/>
+        <v>1632</v>
       </c>
       <c r="I44" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J44" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K44" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.74</v>
       </c>
       <c r="L44" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.01</v>
       </c>
       <c r="M44" s="4">
-        <f t="shared" si="8"/>
-        <v>444</v>
+        <f t="shared" si="9"/>
+        <v>1632</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>43</v>
       </c>
       <c r="B45" s="1">
@@ -2674,33 +2674,33 @@
         <v>0.55000000000000027</v>
       </c>
       <c r="G45" s="12">
-        <f t="shared" si="14"/>
-        <v>449</v>
+        <f t="shared" si="5"/>
+        <v>1660</v>
       </c>
       <c r="I45" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J45" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K45" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.73499999999999999</v>
       </c>
       <c r="L45" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="M45" s="4">
-        <f t="shared" si="8"/>
-        <v>449</v>
+        <f t="shared" si="9"/>
+        <v>1660</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>44</v>
       </c>
       <c r="B46" s="1">
@@ -2723,33 +2723,33 @@
         <v>0.55600000000000027</v>
       </c>
       <c r="G46" s="12">
-        <f t="shared" si="14"/>
-        <v>454</v>
+        <f t="shared" si="5"/>
+        <v>1687</v>
       </c>
       <c r="I46" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J46" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K46" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.73</v>
       </c>
       <c r="L46" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.02</v>
       </c>
       <c r="M46" s="4">
-        <f t="shared" si="8"/>
-        <v>454</v>
+        <f t="shared" si="9"/>
+        <v>1687</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>45</v>
       </c>
       <c r="B47" s="1">
@@ -2772,33 +2772,33 @@
         <v>0.56200000000000028</v>
       </c>
       <c r="G47" s="12">
-        <f t="shared" si="14"/>
-        <v>460</v>
+        <f t="shared" si="5"/>
+        <v>1714</v>
       </c>
       <c r="I47" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J47" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K47" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.72499999999999998</v>
       </c>
       <c r="L47" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M47" s="4">
-        <f t="shared" si="8"/>
-        <v>460</v>
+        <f t="shared" si="9"/>
+        <v>1714</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>46</v>
       </c>
       <c r="B48" s="1">
@@ -2821,33 +2821,33 @@
         <v>0.56800000000000028</v>
       </c>
       <c r="G48" s="12">
-        <f t="shared" si="14"/>
-        <v>465</v>
+        <f t="shared" si="5"/>
+        <v>1741</v>
       </c>
       <c r="I48" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J48" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K48" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.72</v>
       </c>
       <c r="L48" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.03</v>
       </c>
       <c r="M48" s="4">
-        <f t="shared" si="8"/>
-        <v>465</v>
+        <f t="shared" si="9"/>
+        <v>1741</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>47</v>
       </c>
       <c r="B49" s="1">
@@ -2870,33 +2870,33 @@
         <v>0.57400000000000029</v>
       </c>
       <c r="G49" s="12">
-        <f t="shared" si="14"/>
-        <v>470</v>
+        <f t="shared" si="5"/>
+        <v>1767</v>
       </c>
       <c r="I49" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J49" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K49" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.71499999999999997</v>
       </c>
       <c r="L49" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="M49" s="4">
-        <f t="shared" si="8"/>
-        <v>470</v>
+        <f t="shared" si="9"/>
+        <v>1767</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>48</v>
       </c>
       <c r="B50" s="1">
@@ -2919,33 +2919,33 @@
         <v>0.58000000000000029</v>
       </c>
       <c r="G50" s="12">
-        <f t="shared" si="14"/>
-        <v>475</v>
+        <f t="shared" si="5"/>
+        <v>1793</v>
       </c>
       <c r="I50" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J50" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K50" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.71</v>
       </c>
       <c r="L50" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
       <c r="M50" s="4">
-        <f t="shared" si="8"/>
-        <v>475</v>
+        <f t="shared" si="9"/>
+        <v>1793</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>49</v>
       </c>
       <c r="B51" s="1">
@@ -2968,33 +2968,33 @@
         <v>0.5860000000000003</v>
       </c>
       <c r="G51" s="12">
-        <f t="shared" si="14"/>
-        <v>481</v>
+        <f t="shared" si="5"/>
+        <v>1818</v>
       </c>
       <c r="I51" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J51" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K51" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.70499999999999996</v>
       </c>
       <c r="L51" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="M51" s="4">
-        <f t="shared" si="8"/>
-        <v>481</v>
+        <f t="shared" si="9"/>
+        <v>1818</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>50</v>
       </c>
       <c r="B52" s="1">
@@ -3017,33 +3017,33 @@
         <v>0.5920000000000003</v>
       </c>
       <c r="G52" s="12">
-        <f t="shared" si="14"/>
-        <v>486</v>
+        <f t="shared" si="5"/>
+        <v>1843</v>
       </c>
       <c r="I52" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J52" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K52" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.7</v>
       </c>
       <c r="L52" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
       <c r="M52" s="4">
-        <f t="shared" si="8"/>
-        <v>486</v>
+        <f t="shared" si="9"/>
+        <v>1843</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>51</v>
       </c>
       <c r="B53" s="1">
@@ -3066,33 +3066,33 @@
         <v>0.59800000000000031</v>
       </c>
       <c r="G53" s="12">
-        <f t="shared" si="14"/>
-        <v>491</v>
+        <f t="shared" si="5"/>
+        <v>1868</v>
       </c>
       <c r="I53" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J53" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K53" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.69499999999999995</v>
       </c>
       <c r="L53" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.5E-2</v>
       </c>
       <c r="M53" s="4">
-        <f t="shared" si="8"/>
-        <v>491</v>
+        <f t="shared" si="9"/>
+        <v>1868</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>52</v>
       </c>
       <c r="B54" s="1">
@@ -3115,33 +3115,33 @@
         <v>0.60400000000000031</v>
       </c>
       <c r="G54" s="12">
-        <f t="shared" si="14"/>
-        <v>496</v>
+        <f t="shared" si="5"/>
+        <v>1892</v>
       </c>
       <c r="I54" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J54" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K54" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.69</v>
       </c>
       <c r="L54" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.06</v>
       </c>
       <c r="M54" s="4">
-        <f t="shared" si="8"/>
-        <v>496</v>
+        <f t="shared" si="9"/>
+        <v>1892</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>53</v>
       </c>
       <c r="B55" s="1">
@@ -3164,33 +3164,33 @@
         <v>0.61000000000000032</v>
       </c>
       <c r="G55" s="12">
-        <f t="shared" si="14"/>
-        <v>502</v>
+        <f t="shared" si="5"/>
+        <v>1916</v>
       </c>
       <c r="I55" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J55" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K55" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.68500000000000005</v>
       </c>
       <c r="L55" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="M55" s="4">
-        <f t="shared" si="8"/>
-        <v>502</v>
+        <f t="shared" si="9"/>
+        <v>1916</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>54</v>
       </c>
       <c r="B56" s="1">
@@ -3213,33 +3213,33 @@
         <v>0.61600000000000033</v>
       </c>
       <c r="G56" s="12">
-        <f t="shared" si="14"/>
-        <v>507</v>
+        <f t="shared" si="5"/>
+        <v>1940</v>
       </c>
       <c r="I56" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J56" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K56" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
       <c r="L56" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="M56" s="4">
-        <f t="shared" si="8"/>
-        <v>507</v>
+        <f t="shared" si="9"/>
+        <v>1940</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>55</v>
       </c>
       <c r="B57" s="1">
@@ -3262,33 +3262,33 @@
         <v>0.62200000000000033</v>
       </c>
       <c r="G57" s="12">
-        <f t="shared" si="14"/>
-        <v>512</v>
+        <f t="shared" si="5"/>
+        <v>1963</v>
       </c>
       <c r="I57" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J57" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K57" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.67500000000000004</v>
       </c>
       <c r="L57" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="M57" s="4">
-        <f t="shared" si="8"/>
-        <v>512</v>
+        <f t="shared" si="9"/>
+        <v>1963</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>56</v>
       </c>
       <c r="B58" s="1">
@@ -3311,33 +3311,33 @@
         <v>0.62800000000000034</v>
       </c>
       <c r="G58" s="12">
-        <f t="shared" si="14"/>
-        <v>517</v>
+        <f t="shared" si="5"/>
+        <v>1985</v>
       </c>
       <c r="I58" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J58" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K58" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.67</v>
       </c>
       <c r="L58" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
       <c r="M58" s="4">
-        <f t="shared" si="8"/>
-        <v>517</v>
+        <f t="shared" si="9"/>
+        <v>1985</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>57</v>
       </c>
       <c r="B59" s="1">
@@ -3360,33 +3360,33 @@
         <v>0.63400000000000034</v>
       </c>
       <c r="G59" s="12">
-        <f t="shared" si="14"/>
-        <v>523</v>
+        <f t="shared" si="5"/>
+        <v>2008</v>
       </c>
       <c r="I59" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J59" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K59" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.66500000000000004</v>
       </c>
       <c r="L59" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="M59" s="4">
-        <f t="shared" si="8"/>
-        <v>523</v>
+        <f t="shared" si="9"/>
+        <v>2008</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>58</v>
       </c>
       <c r="B60" s="1">
@@ -3409,33 +3409,33 @@
         <v>0.64000000000000035</v>
       </c>
       <c r="G60" s="12">
-        <f t="shared" si="14"/>
-        <v>528</v>
+        <f t="shared" si="5"/>
+        <v>2029</v>
       </c>
       <c r="I60" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J60" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K60" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.66</v>
       </c>
       <c r="L60" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.09</v>
       </c>
       <c r="M60" s="4">
-        <f t="shared" si="8"/>
-        <v>528</v>
+        <f t="shared" si="9"/>
+        <v>2029</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>59</v>
       </c>
       <c r="B61" s="1">
@@ -3458,33 +3458,33 @@
         <v>0.64600000000000035</v>
       </c>
       <c r="G61" s="12">
-        <f t="shared" si="14"/>
-        <v>533</v>
+        <f t="shared" si="5"/>
+        <v>2051</v>
       </c>
       <c r="I61" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J61" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="K61" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.65500000000000003</v>
       </c>
       <c r="L61" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="M61" s="4">
-        <f t="shared" si="8"/>
-        <v>533</v>
+        <f t="shared" si="9"/>
+        <v>2051</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>60</v>
       </c>
       <c r="B62" s="1">
@@ -3505,33 +3505,33 @@
         <v>0.65200000000000036</v>
       </c>
       <c r="G62" s="12">
-        <f t="shared" si="14"/>
-        <v>538</v>
+        <f t="shared" si="5"/>
+        <v>2072</v>
       </c>
       <c r="I62" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J62" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
       <c r="K62" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.8</v>
       </c>
       <c r="L62" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M62" s="4">
-        <f t="shared" si="8"/>
-        <v>538</v>
+        <f t="shared" si="9"/>
+        <v>2072</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>61</v>
       </c>
       <c r="B63" s="1">
@@ -3554,33 +3554,33 @@
         <v>0.65800000000000036</v>
       </c>
       <c r="G63" s="12">
-        <f t="shared" si="14"/>
-        <v>544</v>
+        <f t="shared" si="5"/>
+        <v>2092</v>
       </c>
       <c r="I63" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J63" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
       <c r="K63" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.79</v>
       </c>
       <c r="L63" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.01</v>
       </c>
       <c r="M63" s="4">
-        <f t="shared" si="8"/>
-        <v>544</v>
+        <f t="shared" si="9"/>
+        <v>2092</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>62</v>
       </c>
       <c r="B64" s="1">
@@ -3603,33 +3603,33 @@
         <v>0.66400000000000037</v>
       </c>
       <c r="G64" s="12">
-        <f t="shared" si="14"/>
-        <v>549</v>
+        <f t="shared" si="5"/>
+        <v>2112</v>
       </c>
       <c r="I64" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J64" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
       <c r="K64" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.78</v>
       </c>
       <c r="L64" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.02</v>
       </c>
       <c r="M64" s="4">
-        <f t="shared" si="8"/>
-        <v>549</v>
+        <f t="shared" si="9"/>
+        <v>2112</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>63</v>
       </c>
       <c r="B65" s="1">
@@ -3652,33 +3652,33 @@
         <v>0.67000000000000037</v>
       </c>
       <c r="G65" s="12">
-        <f t="shared" si="14"/>
-        <v>554</v>
+        <f t="shared" si="5"/>
+        <v>2132</v>
       </c>
       <c r="I65" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J65" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
       <c r="K65" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.77</v>
       </c>
       <c r="L65" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.03</v>
       </c>
       <c r="M65" s="4">
-        <f t="shared" si="8"/>
-        <v>554</v>
+        <f t="shared" si="9"/>
+        <v>2132</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>64</v>
       </c>
       <c r="B66" s="1">
@@ -3701,33 +3701,33 @@
         <v>0.67500000000000038</v>
       </c>
       <c r="G66" s="12">
-        <f t="shared" si="14"/>
-        <v>559</v>
+        <f t="shared" si="5"/>
+        <v>2151</v>
       </c>
       <c r="I66" s="4">
         <f t="shared" si="20"/>
         <v>10000</v>
       </c>
       <c r="J66" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
       <c r="K66" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.76</v>
       </c>
       <c r="L66" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
       <c r="M66" s="4">
-        <f t="shared" si="8"/>
-        <v>559</v>
+        <f t="shared" si="9"/>
+        <v>2151</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>65</v>
       </c>
       <c r="B67" s="1">
@@ -3750,33 +3750,33 @@
         <v>0.68000000000000038</v>
       </c>
       <c r="G67" s="12">
-        <f t="shared" si="14"/>
-        <v>565</v>
+        <f t="shared" si="5"/>
+        <v>2169</v>
       </c>
       <c r="I67" s="4">
         <f t="shared" ref="I67:I101" si="29">SUM(B67:D67)</f>
         <v>10000</v>
       </c>
       <c r="J67" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
       <c r="K67" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
       <c r="L67" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
       <c r="M67" s="4">
-        <f t="shared" si="8"/>
-        <v>565</v>
+        <f t="shared" si="9"/>
+        <v>2169</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>66</v>
       </c>
       <c r="B68" s="1">
@@ -3799,33 +3799,33 @@
         <v>0.68500000000000039</v>
       </c>
       <c r="G68" s="12">
-        <f t="shared" si="14"/>
-        <v>570</v>
+        <f t="shared" ref="G68:G101" si="30">ROUND(300 + (2500-300) * SIN( (A68-1) / 99 * PI() / 2 ), 0)</f>
+        <v>2188</v>
       </c>
       <c r="I68" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J68" s="14">
-        <f t="shared" ref="J68:J100" si="30">B68/10000</f>
+        <f t="shared" ref="J68:J100" si="31">B68/10000</f>
         <v>0.2</v>
       </c>
       <c r="K68" s="14">
-        <f t="shared" ref="K68:K100" si="31">C68/10000</f>
+        <f t="shared" ref="K68:K100" si="32">C68/10000</f>
         <v>0.74</v>
       </c>
       <c r="L68" s="14">
-        <f t="shared" ref="L68:L100" si="32">D68/10000</f>
+        <f t="shared" ref="L68:L100" si="33">D68/10000</f>
         <v>0.06</v>
       </c>
       <c r="M68" s="4">
-        <f t="shared" ref="M68:M100" si="33">G68</f>
-        <v>570</v>
+        <f t="shared" ref="M68:M100" si="34">G68</f>
+        <v>2188</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
-        <f t="shared" ref="A69:A74" si="34">A68+1</f>
+        <f t="shared" ref="A69:A74" si="35">A68+1</f>
         <v>67</v>
       </c>
       <c r="B69" s="1">
@@ -3848,33 +3848,33 @@
         <v>0.69000000000000039</v>
       </c>
       <c r="G69" s="12">
-        <f t="shared" ref="G69:G101" si="35">150+ROUNDUP(A69*3.5,0)+ROUNDUP(G68/3,0)</f>
-        <v>575</v>
+        <f t="shared" si="30"/>
+        <v>2205</v>
       </c>
       <c r="I69" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J69" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2</v>
       </c>
       <c r="K69" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.73</v>
       </c>
       <c r="L69" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="M69" s="4">
-        <f t="shared" si="33"/>
-        <v>575</v>
+        <f t="shared" si="34"/>
+        <v>2205</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>68</v>
       </c>
       <c r="B70" s="1">
@@ -3897,33 +3897,33 @@
         <v>0.6950000000000004</v>
       </c>
       <c r="G70" s="12">
-        <f t="shared" si="35"/>
-        <v>580</v>
+        <f t="shared" si="30"/>
+        <v>2222</v>
       </c>
       <c r="I70" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J70" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2</v>
       </c>
       <c r="K70" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.72</v>
       </c>
       <c r="L70" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.08</v>
       </c>
       <c r="M70" s="4">
-        <f t="shared" si="33"/>
-        <v>580</v>
+        <f t="shared" si="34"/>
+        <v>2222</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>69</v>
       </c>
       <c r="B71" s="1">
@@ -3946,33 +3946,33 @@
         <v>0.7000000000000004</v>
       </c>
       <c r="G71" s="12">
-        <f t="shared" si="35"/>
-        <v>586</v>
+        <f t="shared" si="30"/>
+        <v>2239</v>
       </c>
       <c r="I71" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J71" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2</v>
       </c>
       <c r="K71" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.71</v>
       </c>
       <c r="L71" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.09</v>
       </c>
       <c r="M71" s="4">
-        <f t="shared" si="33"/>
-        <v>586</v>
+        <f t="shared" si="34"/>
+        <v>2239</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>70</v>
       </c>
       <c r="B72" s="1">
@@ -3995,33 +3995,33 @@
         <v>0.7050000000000004</v>
       </c>
       <c r="G72" s="12">
-        <f t="shared" si="35"/>
-        <v>591</v>
+        <f t="shared" si="30"/>
+        <v>2255</v>
       </c>
       <c r="I72" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J72" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2</v>
       </c>
       <c r="K72" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.7</v>
       </c>
       <c r="L72" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.1</v>
       </c>
       <c r="M72" s="4">
-        <f t="shared" si="33"/>
-        <v>591</v>
+        <f t="shared" si="34"/>
+        <v>2255</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>71</v>
       </c>
       <c r="B73" s="1">
@@ -4044,33 +4044,33 @@
         <v>0.71000000000000041</v>
       </c>
       <c r="G73" s="12">
-        <f t="shared" si="35"/>
-        <v>596</v>
+        <f t="shared" si="30"/>
+        <v>2271</v>
       </c>
       <c r="I73" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J73" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2</v>
       </c>
       <c r="K73" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.69</v>
       </c>
       <c r="L73" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.11</v>
       </c>
       <c r="M73" s="4">
-        <f t="shared" si="33"/>
-        <v>596</v>
+        <f t="shared" si="34"/>
+        <v>2271</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>72</v>
       </c>
       <c r="B74" s="1">
@@ -4093,28 +4093,28 @@
         <v>0.71500000000000041</v>
       </c>
       <c r="G74" s="12">
-        <f t="shared" si="35"/>
-        <v>601</v>
+        <f t="shared" si="30"/>
+        <v>2286</v>
       </c>
       <c r="I74" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J74" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2</v>
       </c>
       <c r="K74" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.68</v>
       </c>
       <c r="L74" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.12</v>
       </c>
       <c r="M74" s="4">
-        <f t="shared" si="33"/>
-        <v>601</v>
+        <f t="shared" si="34"/>
+        <v>2286</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
@@ -4142,28 +4142,28 @@
         <v>0.72000000000000042</v>
       </c>
       <c r="G75" s="12">
-        <f t="shared" si="35"/>
-        <v>607</v>
+        <f t="shared" si="30"/>
+        <v>2301</v>
       </c>
       <c r="I75" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J75" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2</v>
       </c>
       <c r="K75" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.67</v>
       </c>
       <c r="L75" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.13</v>
       </c>
       <c r="M75" s="4">
-        <f t="shared" si="33"/>
-        <v>607</v>
+        <f t="shared" si="34"/>
+        <v>2301</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
@@ -4191,28 +4191,28 @@
         <v>0.72500000000000042</v>
       </c>
       <c r="G76" s="12">
-        <f t="shared" si="35"/>
-        <v>612</v>
+        <f t="shared" si="30"/>
+        <v>2315</v>
       </c>
       <c r="I76" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J76" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2</v>
       </c>
       <c r="K76" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.66</v>
       </c>
       <c r="L76" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="M76" s="4">
-        <f t="shared" si="33"/>
-        <v>612</v>
+        <f t="shared" si="34"/>
+        <v>2315</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
@@ -4240,28 +4240,28 @@
         <v>0.73000000000000043</v>
       </c>
       <c r="G77" s="12">
-        <f t="shared" si="35"/>
-        <v>617</v>
+        <f t="shared" si="30"/>
+        <v>2329</v>
       </c>
       <c r="I77" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J77" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2</v>
       </c>
       <c r="K77" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.65</v>
       </c>
       <c r="L77" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.15</v>
       </c>
       <c r="M77" s="4">
-        <f t="shared" si="33"/>
-        <v>617</v>
+        <f t="shared" si="34"/>
+        <v>2329</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
@@ -4289,28 +4289,28 @@
         <v>0.73500000000000043</v>
       </c>
       <c r="G78" s="12">
-        <f t="shared" si="35"/>
-        <v>622</v>
+        <f t="shared" si="30"/>
+        <v>2342</v>
       </c>
       <c r="I78" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J78" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2</v>
       </c>
       <c r="K78" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.64</v>
       </c>
       <c r="L78" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.16</v>
       </c>
       <c r="M78" s="4">
-        <f t="shared" si="33"/>
-        <v>622</v>
+        <f t="shared" si="34"/>
+        <v>2342</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.3">
@@ -4338,28 +4338,28 @@
         <v>0.74000000000000044</v>
       </c>
       <c r="G79" s="12">
-        <f t="shared" si="35"/>
-        <v>628</v>
+        <f t="shared" si="30"/>
+        <v>2355</v>
       </c>
       <c r="I79" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J79" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2</v>
       </c>
       <c r="K79" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.63</v>
       </c>
       <c r="L79" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.17</v>
       </c>
       <c r="M79" s="4">
-        <f t="shared" si="33"/>
-        <v>628</v>
+        <f t="shared" si="34"/>
+        <v>2355</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
@@ -4387,28 +4387,28 @@
         <v>0.74500000000000044</v>
       </c>
       <c r="G80" s="12">
-        <f t="shared" si="35"/>
-        <v>633</v>
+        <f t="shared" si="30"/>
+        <v>2367</v>
       </c>
       <c r="I80" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J80" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2</v>
       </c>
       <c r="K80" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.62</v>
       </c>
       <c r="L80" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.18</v>
       </c>
       <c r="M80" s="4">
-        <f t="shared" si="33"/>
-        <v>633</v>
+        <f t="shared" si="34"/>
+        <v>2367</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
@@ -4436,28 +4436,28 @@
         <v>0.75000000000000044</v>
       </c>
       <c r="G81" s="12">
-        <f t="shared" si="35"/>
-        <v>638</v>
+        <f t="shared" si="30"/>
+        <v>2379</v>
       </c>
       <c r="I81" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J81" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2</v>
       </c>
       <c r="K81" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.61</v>
       </c>
       <c r="L81" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.19</v>
       </c>
       <c r="M81" s="4">
-        <f t="shared" si="33"/>
-        <v>638</v>
+        <f t="shared" si="34"/>
+        <v>2379</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
@@ -4483,28 +4483,28 @@
         <v>0.75500000000000045</v>
       </c>
       <c r="G82" s="12">
-        <f t="shared" si="35"/>
-        <v>643</v>
+        <f t="shared" si="30"/>
+        <v>2390</v>
       </c>
       <c r="I82" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J82" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.15</v>
       </c>
       <c r="K82" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.85</v>
       </c>
       <c r="L82" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M82" s="4">
-        <f t="shared" si="33"/>
-        <v>643</v>
+        <f t="shared" si="34"/>
+        <v>2390</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
@@ -4532,28 +4532,28 @@
         <v>0.76000000000000045</v>
       </c>
       <c r="G83" s="12">
-        <f t="shared" si="35"/>
-        <v>649</v>
+        <f t="shared" si="30"/>
+        <v>2401</v>
       </c>
       <c r="I83" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J83" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.15</v>
       </c>
       <c r="K83" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.82899999999999996</v>
       </c>
       <c r="L83" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="M83" s="4">
-        <f t="shared" si="33"/>
-        <v>649</v>
+        <f t="shared" si="34"/>
+        <v>2401</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
@@ -4581,28 +4581,28 @@
         <v>0.76300000000000046</v>
       </c>
       <c r="G84" s="12">
-        <f t="shared" si="35"/>
-        <v>654</v>
+        <f t="shared" si="30"/>
+        <v>2411</v>
       </c>
       <c r="I84" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J84" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.15</v>
       </c>
       <c r="K84" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.80800000000000005</v>
       </c>
       <c r="L84" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="M84" s="4">
-        <f t="shared" si="33"/>
-        <v>654</v>
+        <f t="shared" si="34"/>
+        <v>2411</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.3">
@@ -4630,28 +4630,28 @@
         <v>0.76600000000000046</v>
       </c>
       <c r="G85" s="12">
-        <f t="shared" si="35"/>
-        <v>659</v>
+        <f t="shared" si="30"/>
+        <v>2420</v>
       </c>
       <c r="I85" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J85" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.15</v>
       </c>
       <c r="K85" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.78700000000000003</v>
       </c>
       <c r="L85" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>6.3E-2</v>
       </c>
       <c r="M85" s="4">
-        <f t="shared" si="33"/>
-        <v>659</v>
+        <f t="shared" si="34"/>
+        <v>2420</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.3">
@@ -4679,28 +4679,28 @@
         <v>0.76900000000000046</v>
       </c>
       <c r="G86" s="12">
-        <f t="shared" si="35"/>
-        <v>664</v>
+        <f t="shared" si="30"/>
+        <v>2429</v>
       </c>
       <c r="I86" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J86" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.15</v>
       </c>
       <c r="K86" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.76600000000000001</v>
       </c>
       <c r="L86" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="M86" s="4">
-        <f t="shared" si="33"/>
-        <v>664</v>
+        <f t="shared" si="34"/>
+        <v>2429</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
@@ -4728,28 +4728,28 @@
         <v>0.77200000000000046</v>
       </c>
       <c r="G87" s="12">
-        <f t="shared" si="35"/>
-        <v>670</v>
+        <f t="shared" si="30"/>
+        <v>2438</v>
       </c>
       <c r="I87" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J87" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.15</v>
       </c>
       <c r="K87" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.745</v>
       </c>
       <c r="L87" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.105</v>
       </c>
       <c r="M87" s="4">
-        <f t="shared" si="33"/>
-        <v>670</v>
+        <f t="shared" si="34"/>
+        <v>2438</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
@@ -4777,28 +4777,28 @@
         <v>0.77500000000000047</v>
       </c>
       <c r="G88" s="12">
-        <f t="shared" si="35"/>
-        <v>675</v>
+        <f t="shared" si="30"/>
+        <v>2446</v>
       </c>
       <c r="I88" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J88" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.15</v>
       </c>
       <c r="K88" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.72399999999999998</v>
       </c>
       <c r="L88" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.126</v>
       </c>
       <c r="M88" s="4">
-        <f t="shared" si="33"/>
-        <v>675</v>
+        <f t="shared" si="34"/>
+        <v>2446</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
@@ -4826,28 +4826,28 @@
         <v>0.77800000000000047</v>
       </c>
       <c r="G89" s="12">
-        <f t="shared" si="35"/>
-        <v>680</v>
+        <f t="shared" si="30"/>
+        <v>2453</v>
       </c>
       <c r="I89" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J89" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.15</v>
       </c>
       <c r="K89" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.70299999999999996</v>
       </c>
       <c r="L89" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.14699999999999999</v>
       </c>
       <c r="M89" s="4">
-        <f t="shared" si="33"/>
-        <v>680</v>
+        <f t="shared" si="34"/>
+        <v>2453</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
@@ -4875,28 +4875,28 @@
         <v>0.78100000000000047</v>
       </c>
       <c r="G90" s="12">
-        <f t="shared" si="35"/>
-        <v>685</v>
+        <f t="shared" si="30"/>
+        <v>2460</v>
       </c>
       <c r="I90" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J90" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.15</v>
       </c>
       <c r="K90" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.68200000000000005</v>
       </c>
       <c r="L90" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.16800000000000001</v>
       </c>
       <c r="M90" s="4">
-        <f t="shared" si="33"/>
-        <v>685</v>
+        <f t="shared" si="34"/>
+        <v>2460</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
@@ -4924,28 +4924,28 @@
         <v>0.78400000000000047</v>
       </c>
       <c r="G91" s="12">
-        <f t="shared" si="35"/>
-        <v>691</v>
+        <f t="shared" si="30"/>
+        <v>2467</v>
       </c>
       <c r="I91" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J91" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.15</v>
       </c>
       <c r="K91" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.66100000000000003</v>
       </c>
       <c r="L91" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.189</v>
       </c>
       <c r="M91" s="4">
-        <f t="shared" si="33"/>
-        <v>691</v>
+        <f t="shared" si="34"/>
+        <v>2467</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
@@ -4954,11 +4954,11 @@
         <v>90</v>
       </c>
       <c r="B92" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="C92" s="1">
-        <f t="shared" si="37"/>
-        <v>6400</v>
+        <f>10000-B92-D92</f>
+        <v>6900</v>
       </c>
       <c r="D92" s="4">
         <f t="shared" si="38"/>
@@ -4973,28 +4973,28 @@
         <v>0.78700000000000048</v>
       </c>
       <c r="G92" s="12">
-        <f t="shared" si="35"/>
-        <v>696</v>
+        <f t="shared" si="30"/>
+        <v>2472</v>
       </c>
       <c r="I92" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J92" s="14">
-        <f t="shared" si="30"/>
-        <v>0.15</v>
+        <f t="shared" si="31"/>
+        <v>0.1</v>
       </c>
       <c r="K92" s="14">
-        <f t="shared" si="31"/>
-        <v>0.64</v>
+        <f t="shared" si="32"/>
+        <v>0.69</v>
       </c>
       <c r="L92" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.21</v>
       </c>
       <c r="M92" s="4">
-        <f t="shared" si="33"/>
-        <v>696</v>
+        <f t="shared" si="34"/>
+        <v>2472</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
@@ -5003,15 +5003,15 @@
         <v>91</v>
       </c>
       <c r="B93" s="1">
-        <v>1500</v>
+        <v>900</v>
       </c>
       <c r="C93" s="1">
-        <f t="shared" si="37"/>
-        <v>6190</v>
+        <f t="shared" ref="C93:C101" si="41">10000-B93-D93</f>
+        <v>6335</v>
       </c>
       <c r="D93" s="4">
-        <f t="shared" si="38"/>
-        <v>2310</v>
+        <f>D92+210+A93*5</f>
+        <v>2765</v>
       </c>
       <c r="E93" s="4">
         <f t="shared" si="39"/>
@@ -5022,28 +5022,28 @@
         <v>0.79000000000000048</v>
       </c>
       <c r="G93" s="12">
-        <f t="shared" si="35"/>
-        <v>701</v>
+        <f t="shared" si="30"/>
+        <v>2478</v>
       </c>
       <c r="I93" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J93" s="14">
-        <f t="shared" si="30"/>
-        <v>0.15</v>
+        <f t="shared" si="31"/>
+        <v>0.09</v>
       </c>
       <c r="K93" s="14">
-        <f t="shared" si="31"/>
-        <v>0.61899999999999999</v>
+        <f t="shared" si="32"/>
+        <v>0.63349999999999995</v>
       </c>
       <c r="L93" s="14">
-        <f t="shared" si="32"/>
-        <v>0.23100000000000001</v>
+        <f t="shared" si="33"/>
+        <v>0.27650000000000002</v>
       </c>
       <c r="M93" s="4">
-        <f t="shared" si="33"/>
-        <v>701</v>
+        <f t="shared" si="34"/>
+        <v>2478</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.3">
@@ -5052,15 +5052,15 @@
         <v>92</v>
       </c>
       <c r="B94" s="1">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="C94" s="1">
-        <f t="shared" si="37"/>
-        <v>5980</v>
+        <f t="shared" si="41"/>
+        <v>5765</v>
       </c>
       <c r="D94" s="4">
-        <f t="shared" si="38"/>
-        <v>2520</v>
+        <f t="shared" ref="D94:D101" si="42">D93+210+A94*5</f>
+        <v>3435</v>
       </c>
       <c r="E94" s="4">
         <f t="shared" si="39"/>
@@ -5071,45 +5071,45 @@
         <v>0.79300000000000048</v>
       </c>
       <c r="G94" s="12">
-        <f t="shared" si="35"/>
-        <v>706</v>
+        <f t="shared" si="30"/>
+        <v>2482</v>
       </c>
       <c r="I94" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J94" s="14">
-        <f t="shared" si="30"/>
-        <v>0.15</v>
+        <f t="shared" si="31"/>
+        <v>0.08</v>
       </c>
       <c r="K94" s="14">
-        <f t="shared" si="31"/>
-        <v>0.59799999999999998</v>
+        <f t="shared" si="32"/>
+        <v>0.57650000000000001</v>
       </c>
       <c r="L94" s="14">
-        <f t="shared" si="32"/>
-        <v>0.252</v>
+        <f t="shared" si="33"/>
+        <v>0.34350000000000003</v>
       </c>
       <c r="M94" s="4">
-        <f t="shared" si="33"/>
-        <v>706</v>
+        <f t="shared" si="34"/>
+        <v>2482</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
-        <f t="shared" ref="A95:A102" si="41">A94+1</f>
+        <f t="shared" ref="A95:A102" si="43">A94+1</f>
         <v>93</v>
       </c>
       <c r="B95" s="1">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="C95" s="1">
-        <f t="shared" si="37"/>
-        <v>5770</v>
+        <f t="shared" si="41"/>
+        <v>5190</v>
       </c>
       <c r="D95" s="4">
-        <f t="shared" si="38"/>
-        <v>2730</v>
+        <f t="shared" si="42"/>
+        <v>4110</v>
       </c>
       <c r="E95" s="4">
         <f t="shared" si="39"/>
@@ -5120,45 +5120,45 @@
         <v>0.79600000000000048</v>
       </c>
       <c r="G95" s="12">
-        <f t="shared" si="35"/>
-        <v>712</v>
+        <f t="shared" si="30"/>
+        <v>2486</v>
       </c>
       <c r="I95" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J95" s="14">
-        <f t="shared" si="30"/>
-        <v>0.15</v>
+        <f t="shared" si="31"/>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K95" s="14">
-        <f t="shared" si="31"/>
-        <v>0.57699999999999996</v>
+        <f t="shared" si="32"/>
+        <v>0.51900000000000002</v>
       </c>
       <c r="L95" s="14">
-        <f t="shared" si="32"/>
-        <v>0.27300000000000002</v>
+        <f t="shared" si="33"/>
+        <v>0.41099999999999998</v>
       </c>
       <c r="M95" s="4">
-        <f t="shared" si="33"/>
-        <v>712</v>
+        <f t="shared" si="34"/>
+        <v>2486</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
+        <f t="shared" si="43"/>
+        <v>94</v>
+      </c>
+      <c r="B96" s="1">
+        <v>600</v>
+      </c>
+      <c r="C96" s="1">
         <f t="shared" si="41"/>
-        <v>94</v>
-      </c>
-      <c r="B96" s="1">
-        <v>1500</v>
-      </c>
-      <c r="C96" s="1">
-        <f t="shared" si="37"/>
-        <v>5560</v>
+        <v>4610</v>
       </c>
       <c r="D96" s="4">
-        <f t="shared" si="38"/>
-        <v>2940</v>
+        <f t="shared" si="42"/>
+        <v>4790</v>
       </c>
       <c r="E96" s="4">
         <f t="shared" si="39"/>
@@ -5169,45 +5169,45 @@
         <v>0.79900000000000049</v>
       </c>
       <c r="G96" s="12">
-        <f t="shared" si="35"/>
-        <v>717</v>
+        <f t="shared" si="30"/>
+        <v>2490</v>
       </c>
       <c r="I96" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J96" s="14">
-        <f t="shared" si="30"/>
-        <v>0.15</v>
+        <f t="shared" si="31"/>
+        <v>0.06</v>
       </c>
       <c r="K96" s="14">
-        <f t="shared" si="31"/>
-        <v>0.55600000000000005</v>
+        <f t="shared" si="32"/>
+        <v>0.46100000000000002</v>
       </c>
       <c r="L96" s="14">
-        <f t="shared" si="32"/>
-        <v>0.29399999999999998</v>
+        <f t="shared" si="33"/>
+        <v>0.47899999999999998</v>
       </c>
       <c r="M96" s="4">
-        <f t="shared" si="33"/>
-        <v>717</v>
+        <f t="shared" si="34"/>
+        <v>2490</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
+        <f t="shared" si="43"/>
+        <v>95</v>
+      </c>
+      <c r="B97" s="1">
+        <v>500</v>
+      </c>
+      <c r="C97" s="1">
         <f t="shared" si="41"/>
-        <v>95</v>
-      </c>
-      <c r="B97" s="1">
-        <v>1500</v>
-      </c>
-      <c r="C97" s="1">
-        <f t="shared" si="37"/>
-        <v>5350</v>
+        <v>4025</v>
       </c>
       <c r="D97" s="4">
-        <f t="shared" si="38"/>
-        <v>3150</v>
+        <f t="shared" si="42"/>
+        <v>5475</v>
       </c>
       <c r="E97" s="4">
         <f t="shared" si="39"/>
@@ -5218,45 +5218,45 @@
         <v>0.80200000000000049</v>
       </c>
       <c r="G97" s="12">
-        <f t="shared" si="35"/>
-        <v>722</v>
+        <f t="shared" si="30"/>
+        <v>2493</v>
       </c>
       <c r="I97" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J97" s="14">
-        <f t="shared" si="30"/>
-        <v>0.15</v>
+        <f t="shared" si="31"/>
+        <v>0.05</v>
       </c>
       <c r="K97" s="14">
-        <f t="shared" si="31"/>
-        <v>0.53500000000000003</v>
+        <f t="shared" si="32"/>
+        <v>0.40250000000000002</v>
       </c>
       <c r="L97" s="14">
-        <f t="shared" si="32"/>
-        <v>0.315</v>
+        <f t="shared" si="33"/>
+        <v>0.54749999999999999</v>
       </c>
       <c r="M97" s="4">
-        <f t="shared" si="33"/>
-        <v>722</v>
+        <f t="shared" si="34"/>
+        <v>2493</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
+        <f t="shared" si="43"/>
+        <v>96</v>
+      </c>
+      <c r="B98" s="1">
+        <v>400</v>
+      </c>
+      <c r="C98" s="1">
         <f t="shared" si="41"/>
-        <v>96</v>
-      </c>
-      <c r="B98" s="1">
-        <v>1500</v>
-      </c>
-      <c r="C98" s="1">
-        <f t="shared" si="37"/>
-        <v>5140</v>
+        <v>3435</v>
       </c>
       <c r="D98" s="4">
-        <f t="shared" si="38"/>
-        <v>3360</v>
+        <f t="shared" si="42"/>
+        <v>6165</v>
       </c>
       <c r="E98" s="4">
         <f t="shared" si="39"/>
@@ -5267,45 +5267,45 @@
         <v>0.80500000000000049</v>
       </c>
       <c r="G98" s="12">
-        <f t="shared" si="35"/>
-        <v>727</v>
+        <f t="shared" si="30"/>
+        <v>2496</v>
       </c>
       <c r="I98" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J98" s="14">
-        <f t="shared" si="30"/>
-        <v>0.15</v>
+        <f t="shared" si="31"/>
+        <v>0.04</v>
       </c>
       <c r="K98" s="14">
-        <f t="shared" si="31"/>
-        <v>0.51400000000000001</v>
+        <f t="shared" si="32"/>
+        <v>0.34350000000000003</v>
       </c>
       <c r="L98" s="14">
-        <f t="shared" si="32"/>
-        <v>0.33600000000000002</v>
+        <f t="shared" si="33"/>
+        <v>0.61650000000000005</v>
       </c>
       <c r="M98" s="4">
-        <f t="shared" si="33"/>
-        <v>727</v>
+        <f t="shared" si="34"/>
+        <v>2496</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
+        <f t="shared" si="43"/>
+        <v>97</v>
+      </c>
+      <c r="B99" s="1">
+        <v>300</v>
+      </c>
+      <c r="C99" s="1">
         <f t="shared" si="41"/>
-        <v>97</v>
-      </c>
-      <c r="B99" s="1">
-        <v>1500</v>
-      </c>
-      <c r="C99" s="1">
-        <f t="shared" si="37"/>
-        <v>4930</v>
+        <v>2840</v>
       </c>
       <c r="D99" s="4">
-        <f t="shared" si="38"/>
-        <v>3570</v>
+        <f t="shared" si="42"/>
+        <v>6860</v>
       </c>
       <c r="E99" s="4">
         <f t="shared" si="39"/>
@@ -5316,45 +5316,45 @@
         <v>0.8080000000000005</v>
       </c>
       <c r="G99" s="12">
-        <f t="shared" si="35"/>
-        <v>733</v>
+        <f t="shared" si="30"/>
+        <v>2498</v>
       </c>
       <c r="I99" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J99" s="14">
-        <f t="shared" si="30"/>
-        <v>0.15</v>
+        <f t="shared" si="31"/>
+        <v>0.03</v>
       </c>
       <c r="K99" s="14">
-        <f t="shared" si="31"/>
-        <v>0.49299999999999999</v>
+        <f t="shared" si="32"/>
+        <v>0.28399999999999997</v>
       </c>
       <c r="L99" s="14">
-        <f t="shared" si="32"/>
-        <v>0.35699999999999998</v>
+        <f t="shared" si="33"/>
+        <v>0.68600000000000005</v>
       </c>
       <c r="M99" s="4">
-        <f t="shared" si="33"/>
-        <v>733</v>
+        <f t="shared" si="34"/>
+        <v>2498</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
+        <f t="shared" si="43"/>
+        <v>98</v>
+      </c>
+      <c r="B100" s="1">
+        <v>200</v>
+      </c>
+      <c r="C100" s="1">
         <f t="shared" si="41"/>
-        <v>98</v>
-      </c>
-      <c r="B100" s="1">
-        <v>1500</v>
-      </c>
-      <c r="C100" s="1">
-        <f t="shared" si="37"/>
-        <v>4720</v>
+        <v>2240</v>
       </c>
       <c r="D100" s="4">
-        <f t="shared" si="38"/>
-        <v>3780</v>
+        <f t="shared" si="42"/>
+        <v>7560</v>
       </c>
       <c r="E100" s="4">
         <f t="shared" si="39"/>
@@ -5365,45 +5365,45 @@
         <v>0.8110000000000005</v>
       </c>
       <c r="G100" s="12">
-        <f t="shared" si="35"/>
-        <v>738</v>
+        <f t="shared" si="30"/>
+        <v>2499</v>
       </c>
       <c r="I100" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J100" s="14">
-        <f t="shared" si="30"/>
-        <v>0.15</v>
+        <f t="shared" si="31"/>
+        <v>0.02</v>
       </c>
       <c r="K100" s="14">
-        <f t="shared" si="31"/>
-        <v>0.47199999999999998</v>
+        <f t="shared" si="32"/>
+        <v>0.224</v>
       </c>
       <c r="L100" s="14">
-        <f t="shared" si="32"/>
-        <v>0.378</v>
+        <f t="shared" si="33"/>
+        <v>0.75600000000000001</v>
       </c>
       <c r="M100" s="4">
-        <f t="shared" si="33"/>
-        <v>738</v>
+        <f t="shared" si="34"/>
+        <v>2499</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
+        <f t="shared" si="43"/>
+        <v>99</v>
+      </c>
+      <c r="B101" s="1">
+        <v>100</v>
+      </c>
+      <c r="C101" s="1">
         <f t="shared" si="41"/>
-        <v>99</v>
-      </c>
-      <c r="B101" s="1">
-        <v>1500</v>
-      </c>
-      <c r="C101" s="1">
-        <f t="shared" si="37"/>
-        <v>4510</v>
+        <v>1635</v>
       </c>
       <c r="D101" s="4">
-        <f t="shared" si="38"/>
-        <v>3990</v>
+        <f t="shared" si="42"/>
+        <v>8265</v>
       </c>
       <c r="E101" s="4">
         <f t="shared" si="39"/>
@@ -5414,33 +5414,33 @@
         <v>0.8140000000000005</v>
       </c>
       <c r="G101" s="12">
-        <f t="shared" si="35"/>
-        <v>743</v>
+        <f t="shared" si="30"/>
+        <v>2500</v>
       </c>
       <c r="I101" s="4">
         <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="J101" s="14">
-        <f t="shared" ref="J101" si="42">B101/10000</f>
-        <v>0.15</v>
+        <f t="shared" ref="J101" si="44">B101/10000</f>
+        <v>0.01</v>
       </c>
       <c r="K101" s="14">
-        <f t="shared" ref="K101" si="43">C101/10000</f>
-        <v>0.45100000000000001</v>
+        <f t="shared" ref="K101" si="45">C101/10000</f>
+        <v>0.16350000000000001</v>
       </c>
       <c r="L101" s="14">
-        <f t="shared" ref="L101" si="44">D101/10000</f>
-        <v>0.39900000000000002</v>
+        <f t="shared" ref="L101" si="46">D101/10000</f>
+        <v>0.82650000000000001</v>
       </c>
       <c r="M101" s="4">
-        <f t="shared" ref="M101" si="45">G101</f>
-        <v>743</v>
+        <f t="shared" ref="M101" si="47">G101</f>
+        <v>2500</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>100</v>
       </c>
       <c r="B102" s="5">
